--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574675</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135574646</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135574683</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135574630</v>
       </c>
       <c r="B5" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135574631</v>
       </c>
       <c r="B6" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135574632</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135574633</v>
       </c>
       <c r="B8" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135574636</v>
       </c>
       <c r="B9" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135574637</v>
       </c>
       <c r="B10" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135574642</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135574658</v>
       </c>
       <c r="B12" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135574662</v>
       </c>
       <c r="B13" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135574686</v>
       </c>
       <c r="B14" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135574687</v>
       </c>
       <c r="B15" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135574664</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>135574690</v>
       </c>
       <c r="B21" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>135574634</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>135574639</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>135574641</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>135574644</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135574647</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>135574648</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135574650</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135574651</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135574652</v>
       </c>
       <c r="B32" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135574655</v>
       </c>
       <c r="B33" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135574656</v>
       </c>
       <c r="B34" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135574660</v>
       </c>
       <c r="B35" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135574661</v>
       </c>
       <c r="B36" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135574663</v>
       </c>
       <c r="B37" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135574672</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135574674</v>
       </c>
       <c r="B39" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135574676</v>
       </c>
       <c r="B40" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135574680</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135574684</v>
       </c>
       <c r="B42" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135574635</v>
       </c>
       <c r="B47" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>135574640</v>
       </c>
       <c r="B48" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135574645</v>
       </c>
       <c r="B49" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>135574649</v>
       </c>
       <c r="B50" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>135574654</v>
       </c>
       <c r="B51" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135574657</v>
       </c>
       <c r="B52" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135574659</v>
       </c>
       <c r="B53" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>135574667</v>
       </c>
       <c r="B54" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135574678</v>
       </c>
       <c r="B56" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>135574681</v>
       </c>
       <c r="B57" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>135574685</v>
       </c>
       <c r="B58" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>135574682</v>
       </c>
       <c r="B59" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574675</v>
       </c>
       <c r="B2" t="n">
-        <v>92848</v>
+        <v>92875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135574646</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135574683</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135574630</v>
       </c>
       <c r="B5" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135574631</v>
       </c>
       <c r="B6" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135574632</v>
       </c>
       <c r="B7" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135574633</v>
       </c>
       <c r="B8" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135574636</v>
       </c>
       <c r="B9" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135574637</v>
       </c>
       <c r="B10" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135574642</v>
       </c>
       <c r="B11" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135574658</v>
       </c>
       <c r="B12" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135574662</v>
       </c>
       <c r="B13" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135574686</v>
       </c>
       <c r="B14" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135574687</v>
       </c>
       <c r="B15" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>135574634</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>135574639</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>135574641</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>135574644</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135574647</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>135574648</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135574650</v>
       </c>
       <c r="B30" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135574651</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135574652</v>
       </c>
       <c r="B32" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135574655</v>
       </c>
       <c r="B33" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135574656</v>
       </c>
       <c r="B34" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135574660</v>
       </c>
       <c r="B35" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135574661</v>
       </c>
       <c r="B36" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135574663</v>
       </c>
       <c r="B37" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135574672</v>
       </c>
       <c r="B38" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135574674</v>
       </c>
       <c r="B39" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135574676</v>
       </c>
       <c r="B40" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135574680</v>
       </c>
       <c r="B41" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135574684</v>
       </c>
       <c r="B42" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135574635</v>
       </c>
       <c r="B47" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>135574640</v>
       </c>
       <c r="B48" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135574645</v>
       </c>
       <c r="B49" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>135574649</v>
       </c>
       <c r="B50" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>135574654</v>
       </c>
       <c r="B51" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135574657</v>
       </c>
       <c r="B52" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135574659</v>
       </c>
       <c r="B53" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>135574667</v>
       </c>
       <c r="B54" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135574678</v>
       </c>
       <c r="B56" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>135574681</v>
       </c>
       <c r="B57" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>135574685</v>
       </c>
       <c r="B58" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>135574682</v>
       </c>
       <c r="B59" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574675</v>
       </c>
       <c r="B2" t="n">
-        <v>92880</v>
+        <v>92882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>135574634</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>135574639</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>135574641</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>135574644</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135574647</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>135574648</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135574650</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135574651</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135574652</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135574655</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135574656</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135574660</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135574661</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135574663</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135574672</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135574674</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135574676</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135574680</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135574684</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135574635</v>
       </c>
       <c r="B47" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>135574640</v>
       </c>
       <c r="B48" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135574645</v>
       </c>
       <c r="B49" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>135574649</v>
       </c>
       <c r="B50" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>135574654</v>
       </c>
       <c r="B51" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135574657</v>
       </c>
       <c r="B52" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135574659</v>
       </c>
       <c r="B53" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>135574667</v>
       </c>
       <c r="B54" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135574678</v>
       </c>
       <c r="B56" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>135574681</v>
       </c>
       <c r="B57" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>135574685</v>
       </c>
       <c r="B58" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>135574682</v>
       </c>
       <c r="B59" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574666</v>
+        <v>135574690</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>58084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,24 +2431,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481606</v>
+        <v>481438</v>
       </c>
       <c r="R17" t="n">
-        <v>7024919</v>
+        <v>7024659</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,12 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,59 +2525,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574666</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574668</v>
+        <v>135574638</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>99193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481600</v>
+        <v>481544</v>
       </c>
       <c r="R18" t="n">
-        <v>7024916</v>
+        <v>7024650</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2599,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,12 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,58 +2637,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574668</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574670</v>
+        <v>135574643</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>99193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481586</v>
+        <v>481579</v>
       </c>
       <c r="R19" t="n">
-        <v>7024911</v>
+        <v>7024692</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2720,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,12 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,56 +2749,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574670</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574677</v>
+        <v>135574634</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481568</v>
+        <v>481508</v>
       </c>
       <c r="R20" t="n">
-        <v>7024870</v>
+        <v>7024656</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2842,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2852,12 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,70 +2861,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574677</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574690</v>
+        <v>135574639</v>
       </c>
       <c r="B21" t="n">
-        <v>58084</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481438</v>
+        <v>481525</v>
       </c>
       <c r="R21" t="n">
-        <v>7024659</v>
+        <v>7024642</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2975,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,38 +2973,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574638</v>
+        <v>135574641</v>
       </c>
       <c r="B22" t="n">
-        <v>99193</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3052,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481544</v>
+        <v>481577</v>
       </c>
       <c r="R22" t="n">
-        <v>7024650</v>
+        <v>7024669</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3087,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3097,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3123,38 +3085,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574643</v>
+        <v>135574644</v>
       </c>
       <c r="B23" t="n">
-        <v>99193</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3126,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481579</v>
+        <v>481577</v>
       </c>
       <c r="R23" t="n">
-        <v>7024692</v>
+        <v>7024691</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3209,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3235,13 +3197,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574634</v>
+        <v>135574647</v>
       </c>
       <c r="B24" t="n">
         <v>99276</v>
@@ -3276,13 +3238,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481508</v>
+        <v>481595</v>
       </c>
       <c r="R24" t="n">
-        <v>7024656</v>
+        <v>7024696</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3311,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,13 +3309,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574639</v>
+        <v>135574648</v>
       </c>
       <c r="B25" t="n">
         <v>99276</v>
@@ -3388,13 +3350,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481525</v>
+        <v>481630</v>
       </c>
       <c r="R25" t="n">
-        <v>7024642</v>
+        <v>7024686</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3423,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,13 +3421,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574641</v>
+        <v>135574650</v>
       </c>
       <c r="B26" t="n">
         <v>99276</v>
@@ -3500,13 +3462,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481577</v>
+        <v>481647</v>
       </c>
       <c r="R26" t="n">
-        <v>7024669</v>
+        <v>7024696</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3535,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3545,7 +3507,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,13 +3538,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574644</v>
+        <v>135574651</v>
       </c>
       <c r="B27" t="n">
         <v>99276</v>
@@ -3612,13 +3579,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481577</v>
+        <v>481676</v>
       </c>
       <c r="R27" t="n">
-        <v>7024691</v>
+        <v>7024717</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3647,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3657,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,13 +3650,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574647</v>
+        <v>135574652</v>
       </c>
       <c r="B28" t="n">
         <v>99276</v>
@@ -3724,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481595</v>
+        <v>481695</v>
       </c>
       <c r="R28" t="n">
-        <v>7024696</v>
+        <v>7024735</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3759,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,13 +3762,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574648</v>
+        <v>135574655</v>
       </c>
       <c r="B29" t="n">
         <v>99276</v>
@@ -3836,10 +3803,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481630</v>
+        <v>481716</v>
       </c>
       <c r="R29" t="n">
-        <v>7024686</v>
+        <v>7024780</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3871,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,13 +3874,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574650</v>
+        <v>135574656</v>
       </c>
       <c r="B30" t="n">
         <v>99276</v>
@@ -3948,13 +3915,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481647</v>
+        <v>481734</v>
       </c>
       <c r="R30" t="n">
-        <v>7024696</v>
+        <v>7024791</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3983,7 +3950,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3993,12 +3960,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4024,13 +3986,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574651</v>
+        <v>135574660</v>
       </c>
       <c r="B31" t="n">
         <v>99276</v>
@@ -4065,13 +4027,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481676</v>
+        <v>481719</v>
       </c>
       <c r="R31" t="n">
-        <v>7024717</v>
+        <v>7024855</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4136,13 +4098,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574652</v>
+        <v>135574661</v>
       </c>
       <c r="B32" t="n">
         <v>99276</v>
@@ -4177,13 +4139,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481695</v>
+        <v>481701</v>
       </c>
       <c r="R32" t="n">
-        <v>7024735</v>
+        <v>7024856</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4212,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4222,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4248,13 +4210,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574655</v>
+        <v>135574663</v>
       </c>
       <c r="B33" t="n">
         <v>99276</v>
@@ -4289,13 +4251,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481716</v>
+        <v>481646</v>
       </c>
       <c r="R33" t="n">
-        <v>7024780</v>
+        <v>7024891</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4324,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4334,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,13 +4322,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574656</v>
+        <v>135574672</v>
       </c>
       <c r="B34" t="n">
         <v>99276</v>
@@ -4401,13 +4363,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481734</v>
+        <v>481561</v>
       </c>
       <c r="R34" t="n">
-        <v>7024791</v>
+        <v>7024902</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,13 +4434,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574660</v>
+        <v>135574674</v>
       </c>
       <c r="B35" t="n">
         <v>99276</v>
@@ -4513,13 +4475,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481719</v>
+        <v>481578</v>
       </c>
       <c r="R35" t="n">
-        <v>7024855</v>
+        <v>7024883</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4548,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4558,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4584,13 +4546,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574661</v>
+        <v>135574676</v>
       </c>
       <c r="B36" t="n">
         <v>99276</v>
@@ -4625,13 +4587,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481701</v>
+        <v>481552</v>
       </c>
       <c r="R36" t="n">
-        <v>7024856</v>
+        <v>7024876</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4660,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4670,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4696,13 +4658,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574663</v>
+        <v>135574680</v>
       </c>
       <c r="B37" t="n">
         <v>99276</v>
@@ -4737,13 +4699,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481646</v>
+        <v>481573</v>
       </c>
       <c r="R37" t="n">
-        <v>7024891</v>
+        <v>7024817</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4772,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4782,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4808,13 +4770,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574672</v>
+        <v>135574684</v>
       </c>
       <c r="B38" t="n">
         <v>99276</v>
@@ -4849,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481561</v>
+        <v>481498</v>
       </c>
       <c r="R38" t="n">
-        <v>7024902</v>
+        <v>7024750</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4884,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4894,7 +4856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4920,13 +4882,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574674</v>
+        <v>135574688</v>
       </c>
       <c r="B39" t="n">
         <v>99276</v>
@@ -4961,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481578</v>
+        <v>481456</v>
       </c>
       <c r="R39" t="n">
-        <v>7024883</v>
+        <v>7024666</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4996,7 +4958,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5006,7 +4968,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5032,13 +4994,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574676</v>
+        <v>135574689</v>
       </c>
       <c r="B40" t="n">
         <v>99276</v>
@@ -5073,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481552</v>
+        <v>481438</v>
       </c>
       <c r="R40" t="n">
-        <v>7024876</v>
+        <v>7024662</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5108,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5118,7 +5080,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,13 +5106,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574680</v>
+        <v>135574691</v>
       </c>
       <c r="B41" t="n">
         <v>99276</v>
@@ -5185,13 +5147,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481573</v>
+        <v>481402</v>
       </c>
       <c r="R41" t="n">
-        <v>7024817</v>
+        <v>7024646</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5220,7 +5182,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5230,7 +5192,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5256,13 +5218,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574684</v>
+        <v>135574692</v>
       </c>
       <c r="B42" t="n">
         <v>99276</v>
@@ -5297,13 +5259,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481498</v>
+        <v>481397</v>
       </c>
       <c r="R42" t="n">
-        <v>7024750</v>
+        <v>7024634</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5332,7 +5294,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5342,7 +5304,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5368,38 +5330,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574688</v>
+        <v>135574635</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>101485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5409,10 +5371,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481456</v>
+        <v>481524</v>
       </c>
       <c r="R43" t="n">
-        <v>7024666</v>
+        <v>7024657</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5444,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5454,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,38 +5442,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574689</v>
+        <v>135574640</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>101485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5521,13 +5483,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481438</v>
+        <v>481545</v>
       </c>
       <c r="R44" t="n">
-        <v>7024662</v>
+        <v>7024654</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5556,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5566,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5592,38 +5554,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574691</v>
+        <v>135574645</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>101485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5633,13 +5595,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481402</v>
+        <v>481577</v>
       </c>
       <c r="R45" t="n">
-        <v>7024646</v>
+        <v>7024692</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5668,7 +5630,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5678,7 +5640,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5704,38 +5666,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574692</v>
+        <v>135574649</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>101485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5745,13 +5707,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481397</v>
+        <v>481625</v>
       </c>
       <c r="R46" t="n">
-        <v>7024634</v>
+        <v>7024693</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5780,7 +5742,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5790,7 +5752,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,13 +5778,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574635</v>
+        <v>135574654</v>
       </c>
       <c r="B47" t="n">
         <v>101485</v>
@@ -5857,10 +5819,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481524</v>
+        <v>481705</v>
       </c>
       <c r="R47" t="n">
-        <v>7024657</v>
+        <v>7024756</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5892,7 +5854,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5902,7 +5864,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5928,13 +5890,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574640</v>
+        <v>135574657</v>
       </c>
       <c r="B48" t="n">
         <v>101485</v>
@@ -5969,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481545</v>
+        <v>481729</v>
       </c>
       <c r="R48" t="n">
-        <v>7024654</v>
+        <v>7024823</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6004,7 +5966,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6014,7 +5976,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6040,13 +6002,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574645</v>
+        <v>135574659</v>
       </c>
       <c r="B49" t="n">
         <v>101485</v>
@@ -6081,10 +6043,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481577</v>
+        <v>481714</v>
       </c>
       <c r="R49" t="n">
-        <v>7024692</v>
+        <v>7024855</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6116,7 +6078,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6126,7 +6088,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6152,13 +6114,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574649</v>
+        <v>135574667</v>
       </c>
       <c r="B50" t="n">
         <v>101485</v>
@@ -6193,10 +6155,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481625</v>
+        <v>481606</v>
       </c>
       <c r="R50" t="n">
-        <v>7024693</v>
+        <v>7024919</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6228,7 +6190,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6238,7 +6200,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,13 +6226,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574654</v>
+        <v>135574673</v>
       </c>
       <c r="B51" t="n">
         <v>101485</v>
@@ -6305,13 +6267,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481705</v>
+        <v>481558</v>
       </c>
       <c r="R51" t="n">
-        <v>7024756</v>
+        <v>7024899</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6340,7 +6302,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6350,7 +6312,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,13 +6338,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574673</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574657</v>
+        <v>135574678</v>
       </c>
       <c r="B52" t="n">
         <v>101485</v>
@@ -6417,10 +6379,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481729</v>
+        <v>481581</v>
       </c>
       <c r="R52" t="n">
-        <v>7024823</v>
+        <v>7024835</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6452,7 +6414,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6462,7 +6424,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6488,13 +6450,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574678</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574659</v>
+        <v>135574681</v>
       </c>
       <c r="B53" t="n">
         <v>101485</v>
@@ -6529,10 +6491,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481714</v>
+        <v>481566</v>
       </c>
       <c r="R53" t="n">
-        <v>7024855</v>
+        <v>7024806</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6564,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6574,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6600,13 +6562,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574681</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574667</v>
+        <v>135574685</v>
       </c>
       <c r="B54" t="n">
         <v>101485</v>
@@ -6641,13 +6603,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481606</v>
+        <v>481499</v>
       </c>
       <c r="R54" t="n">
-        <v>7024919</v>
+        <v>7024746</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6676,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6686,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6712,16 +6674,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574685</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574673</v>
+        <v>135574682</v>
       </c>
       <c r="B55" t="n">
-        <v>101485</v>
+        <v>99553</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6729,21 +6691,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>222812</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6753,13 +6715,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481558</v>
+        <v>481541</v>
       </c>
       <c r="R55" t="n">
-        <v>7024899</v>
+        <v>7024804</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6788,7 +6750,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6798,7 +6760,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6823,454 +6785,6 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135574678</v>
-      </c>
-      <c r="B56" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>481581</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7024835</v>
-      </c>
-      <c r="S56" t="n">
-        <v>4</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135574681</v>
-      </c>
-      <c r="B57" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>481566</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7024806</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135574685</v>
-      </c>
-      <c r="B58" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>481499</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7024746</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135574682</v>
-      </c>
-      <c r="B59" t="n">
-        <v>99553</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>481541</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7024804</v>
-      </c>
-      <c r="S59" t="n">
-        <v>4</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -7332,10 +6846,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574690</v>
+        <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>58084</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,36 +2431,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481438</v>
+        <v>481606</v>
       </c>
       <c r="R17" t="n">
-        <v>7024659</v>
+        <v>7024919</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2487,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,54 +2518,59 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574666</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574638</v>
+        <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>99193</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481544</v>
+        <v>481600</v>
       </c>
       <c r="R18" t="n">
-        <v>7024650</v>
+        <v>7024916</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2609,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,54 +2640,58 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574668</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574643</v>
+        <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>99193</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481579</v>
+        <v>481586</v>
       </c>
       <c r="R19" t="n">
-        <v>7024692</v>
+        <v>7024911</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2713,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2730,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,51 +2761,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574670</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574634</v>
+        <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481508</v>
+        <v>481568</v>
       </c>
       <c r="R20" t="n">
-        <v>7024656</v>
+        <v>7024870</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2825,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2852,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,54 +2883,70 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574677</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574639</v>
+        <v>135574690</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>58084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481525</v>
+        <v>481438</v>
       </c>
       <c r="R21" t="n">
-        <v>7024642</v>
+        <v>7024659</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2937,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2985,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,38 +3011,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574641</v>
+        <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3052,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481577</v>
+        <v>481544</v>
       </c>
       <c r="R22" t="n">
-        <v>7024669</v>
+        <v>7024650</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3049,7 +3087,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3097,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,38 +3123,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574644</v>
+        <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481577</v>
+        <v>481579</v>
       </c>
       <c r="R23" t="n">
-        <v>7024691</v>
+        <v>7024692</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3161,7 +3199,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3209,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,13 +3235,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574647</v>
+        <v>135574634</v>
       </c>
       <c r="B24" t="n">
         <v>99276</v>
@@ -3238,13 +3276,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481595</v>
+        <v>481508</v>
       </c>
       <c r="R24" t="n">
-        <v>7024696</v>
+        <v>7024656</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3273,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,13 +3347,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574648</v>
+        <v>135574639</v>
       </c>
       <c r="B25" t="n">
         <v>99276</v>
@@ -3350,13 +3388,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481630</v>
+        <v>481525</v>
       </c>
       <c r="R25" t="n">
-        <v>7024686</v>
+        <v>7024642</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3385,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3433,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,13 +3459,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574650</v>
+        <v>135574641</v>
       </c>
       <c r="B26" t="n">
         <v>99276</v>
@@ -3462,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481647</v>
+        <v>481577</v>
       </c>
       <c r="R26" t="n">
-        <v>7024696</v>
+        <v>7024669</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3497,7 +3535,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,12 +3545,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,13 +3571,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574651</v>
+        <v>135574644</v>
       </c>
       <c r="B27" t="n">
         <v>99276</v>
@@ -3579,13 +3612,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481676</v>
+        <v>481577</v>
       </c>
       <c r="R27" t="n">
-        <v>7024717</v>
+        <v>7024691</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3614,7 +3647,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3657,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,13 +3683,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574652</v>
+        <v>135574647</v>
       </c>
       <c r="B28" t="n">
         <v>99276</v>
@@ -3691,13 +3724,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481695</v>
+        <v>481595</v>
       </c>
       <c r="R28" t="n">
-        <v>7024735</v>
+        <v>7024696</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3769,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574655</v>
+        <v>135574648</v>
       </c>
       <c r="B29" t="n">
         <v>99276</v>
@@ -3803,10 +3836,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481716</v>
+        <v>481630</v>
       </c>
       <c r="R29" t="n">
-        <v>7024780</v>
+        <v>7024686</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3838,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3881,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3874,13 +3907,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574656</v>
+        <v>135574650</v>
       </c>
       <c r="B30" t="n">
         <v>99276</v>
@@ -3915,13 +3948,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481734</v>
+        <v>481647</v>
       </c>
       <c r="R30" t="n">
-        <v>7024791</v>
+        <v>7024696</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3950,7 +3983,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3960,7 +3993,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,13 +4024,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574660</v>
+        <v>135574651</v>
       </c>
       <c r="B31" t="n">
         <v>99276</v>
@@ -4027,13 +4065,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481719</v>
+        <v>481676</v>
       </c>
       <c r="R31" t="n">
-        <v>7024855</v>
+        <v>7024717</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,7 +4100,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4110,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4098,13 +4136,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574661</v>
+        <v>135574652</v>
       </c>
       <c r="B32" t="n">
         <v>99276</v>
@@ -4139,13 +4177,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481701</v>
+        <v>481695</v>
       </c>
       <c r="R32" t="n">
-        <v>7024856</v>
+        <v>7024735</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4174,7 +4212,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +4222,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,13 +4248,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574663</v>
+        <v>135574655</v>
       </c>
       <c r="B33" t="n">
         <v>99276</v>
@@ -4251,13 +4289,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481646</v>
+        <v>481716</v>
       </c>
       <c r="R33" t="n">
-        <v>7024891</v>
+        <v>7024780</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4286,7 +4324,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4334,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,13 +4360,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574672</v>
+        <v>135574656</v>
       </c>
       <c r="B34" t="n">
         <v>99276</v>
@@ -4363,13 +4401,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481561</v>
+        <v>481734</v>
       </c>
       <c r="R34" t="n">
-        <v>7024902</v>
+        <v>7024791</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4398,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,13 +4472,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574674</v>
+        <v>135574660</v>
       </c>
       <c r="B35" t="n">
         <v>99276</v>
@@ -4475,13 +4513,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481578</v>
+        <v>481719</v>
       </c>
       <c r="R35" t="n">
-        <v>7024883</v>
+        <v>7024855</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4510,7 +4548,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4558,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,13 +4584,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574676</v>
+        <v>135574661</v>
       </c>
       <c r="B36" t="n">
         <v>99276</v>
@@ -4587,13 +4625,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481552</v>
+        <v>481701</v>
       </c>
       <c r="R36" t="n">
-        <v>7024876</v>
+        <v>7024856</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4622,7 +4660,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4670,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4658,13 +4696,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574680</v>
+        <v>135574663</v>
       </c>
       <c r="B37" t="n">
         <v>99276</v>
@@ -4699,13 +4737,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481573</v>
+        <v>481646</v>
       </c>
       <c r="R37" t="n">
-        <v>7024817</v>
+        <v>7024891</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4734,7 +4772,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4782,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4770,13 +4808,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574684</v>
+        <v>135574672</v>
       </c>
       <c r="B38" t="n">
         <v>99276</v>
@@ -4811,10 +4849,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481498</v>
+        <v>481561</v>
       </c>
       <c r="R38" t="n">
-        <v>7024750</v>
+        <v>7024902</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4846,7 +4884,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4894,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,13 +4920,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574688</v>
+        <v>135574674</v>
       </c>
       <c r="B39" t="n">
         <v>99276</v>
@@ -4923,10 +4961,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481456</v>
+        <v>481578</v>
       </c>
       <c r="R39" t="n">
-        <v>7024666</v>
+        <v>7024883</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4958,7 +4996,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +5006,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,13 +5032,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574689</v>
+        <v>135574676</v>
       </c>
       <c r="B40" t="n">
         <v>99276</v>
@@ -5035,10 +5073,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481438</v>
+        <v>481552</v>
       </c>
       <c r="R40" t="n">
-        <v>7024662</v>
+        <v>7024876</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5070,7 +5108,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +5118,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5106,13 +5144,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574691</v>
+        <v>135574680</v>
       </c>
       <c r="B41" t="n">
         <v>99276</v>
@@ -5147,13 +5185,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481402</v>
+        <v>481573</v>
       </c>
       <c r="R41" t="n">
-        <v>7024646</v>
+        <v>7024817</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,7 +5220,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5192,7 +5230,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5218,13 +5256,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574692</v>
+        <v>135574684</v>
       </c>
       <c r="B42" t="n">
         <v>99276</v>
@@ -5259,13 +5297,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481397</v>
+        <v>481498</v>
       </c>
       <c r="R42" t="n">
-        <v>7024634</v>
+        <v>7024750</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5294,7 +5332,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5304,7 +5342,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,38 +5368,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574635</v>
+        <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>101485</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5409,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481524</v>
+        <v>481456</v>
       </c>
       <c r="R43" t="n">
-        <v>7024657</v>
+        <v>7024666</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5406,7 +5444,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5454,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5442,38 +5480,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574640</v>
+        <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>101485</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,13 +5521,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481545</v>
+        <v>481438</v>
       </c>
       <c r="R44" t="n">
-        <v>7024654</v>
+        <v>7024662</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5518,7 +5556,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5566,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5554,38 +5592,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574645</v>
+        <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>101485</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,13 +5633,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481577</v>
+        <v>481402</v>
       </c>
       <c r="R45" t="n">
-        <v>7024692</v>
+        <v>7024646</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5630,7 +5668,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5640,7 +5678,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,38 +5704,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574649</v>
+        <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>101485</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5707,13 +5745,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481625</v>
+        <v>481397</v>
       </c>
       <c r="R46" t="n">
-        <v>7024693</v>
+        <v>7024634</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5742,7 +5780,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5752,7 +5790,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,13 +5816,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574654</v>
+        <v>135574635</v>
       </c>
       <c r="B47" t="n">
         <v>101485</v>
@@ -5819,10 +5857,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481705</v>
+        <v>481524</v>
       </c>
       <c r="R47" t="n">
-        <v>7024756</v>
+        <v>7024657</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5854,7 +5892,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5864,7 +5902,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5890,13 +5928,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574657</v>
+        <v>135574640</v>
       </c>
       <c r="B48" t="n">
         <v>101485</v>
@@ -5931,10 +5969,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481729</v>
+        <v>481545</v>
       </c>
       <c r="R48" t="n">
-        <v>7024823</v>
+        <v>7024654</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5966,7 +6004,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5976,7 +6014,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6002,13 +6040,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574659</v>
+        <v>135574645</v>
       </c>
       <c r="B49" t="n">
         <v>101485</v>
@@ -6043,10 +6081,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481714</v>
+        <v>481577</v>
       </c>
       <c r="R49" t="n">
-        <v>7024855</v>
+        <v>7024692</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6078,7 +6116,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6088,7 +6126,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6114,13 +6152,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574667</v>
+        <v>135574649</v>
       </c>
       <c r="B50" t="n">
         <v>101485</v>
@@ -6155,10 +6193,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481606</v>
+        <v>481625</v>
       </c>
       <c r="R50" t="n">
-        <v>7024919</v>
+        <v>7024693</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6190,7 +6228,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6200,7 +6238,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6226,13 +6264,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574673</v>
+        <v>135574654</v>
       </c>
       <c r="B51" t="n">
         <v>101485</v>
@@ -6267,13 +6305,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481558</v>
+        <v>481705</v>
       </c>
       <c r="R51" t="n">
-        <v>7024899</v>
+        <v>7024756</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6302,7 +6340,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6312,7 +6350,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6338,13 +6376,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574678</v>
+        <v>135574657</v>
       </c>
       <c r="B52" t="n">
         <v>101485</v>
@@ -6379,10 +6417,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481581</v>
+        <v>481729</v>
       </c>
       <c r="R52" t="n">
-        <v>7024835</v>
+        <v>7024823</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6414,7 +6452,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6424,7 +6462,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6450,13 +6488,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574681</v>
+        <v>135574659</v>
       </c>
       <c r="B53" t="n">
         <v>101485</v>
@@ -6491,10 +6529,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481566</v>
+        <v>481714</v>
       </c>
       <c r="R53" t="n">
-        <v>7024806</v>
+        <v>7024855</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6526,7 +6564,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6574,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6562,13 +6600,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574685</v>
+        <v>135574667</v>
       </c>
       <c r="B54" t="n">
         <v>101485</v>
@@ -6603,13 +6641,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481499</v>
+        <v>481606</v>
       </c>
       <c r="R54" t="n">
-        <v>7024746</v>
+        <v>7024919</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6638,7 +6676,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6686,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6674,16 +6712,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574682</v>
+        <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>99553</v>
+        <v>101485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6691,21 +6729,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,13 +6753,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481541</v>
+        <v>481558</v>
       </c>
       <c r="R55" t="n">
-        <v>7024804</v>
+        <v>7024899</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6750,7 +6788,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6760,7 +6798,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6785,6 +6823,454 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574673</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135574678</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>481581</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7024835</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574678</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135574681</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>481566</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7024806</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574681</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135574685</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>481499</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7024746</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574685</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135574682</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99553</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>481541</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7024804</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -6846,6 +7332,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574675</v>
       </c>
       <c r="B2" t="n">
-        <v>92882</v>
+        <v>92897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135574646</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135574683</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135574630</v>
       </c>
       <c r="B5" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135574631</v>
       </c>
       <c r="B6" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135574632</v>
       </c>
       <c r="B7" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135574633</v>
       </c>
       <c r="B8" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135574636</v>
       </c>
       <c r="B9" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135574637</v>
       </c>
       <c r="B10" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135574642</v>
       </c>
       <c r="B11" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135574658</v>
       </c>
       <c r="B12" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135574662</v>
       </c>
       <c r="B13" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135574686</v>
       </c>
       <c r="B14" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135574687</v>
       </c>
       <c r="B15" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135574664</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>135574690</v>
       </c>
       <c r="B21" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>135574634</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>135574639</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>135574641</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>135574644</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135574647</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>135574648</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135574650</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135574651</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135574652</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135574655</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135574656</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135574660</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135574661</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135574663</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135574672</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135574674</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135574676</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135574680</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135574684</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135574635</v>
       </c>
       <c r="B47" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>135574640</v>
       </c>
       <c r="B48" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135574645</v>
       </c>
       <c r="B49" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>135574649</v>
       </c>
       <c r="B50" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>135574654</v>
       </c>
       <c r="B51" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135574657</v>
       </c>
       <c r="B52" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135574659</v>
       </c>
       <c r="B53" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>135574667</v>
       </c>
       <c r="B54" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135574678</v>
       </c>
       <c r="B56" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>135574681</v>
       </c>
       <c r="B57" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>135574685</v>
       </c>
       <c r="B58" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>135574682</v>
       </c>
       <c r="B59" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574666</v>
+        <v>135574690</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>58086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,24 +2431,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481606</v>
+        <v>481438</v>
       </c>
       <c r="R17" t="n">
-        <v>7024919</v>
+        <v>7024659</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,12 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,59 +2525,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574666</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574668</v>
+        <v>135574638</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481600</v>
+        <v>481544</v>
       </c>
       <c r="R18" t="n">
-        <v>7024916</v>
+        <v>7024650</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2599,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,12 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,58 +2637,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574668</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574670</v>
+        <v>135574643</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>99210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481586</v>
+        <v>481579</v>
       </c>
       <c r="R19" t="n">
-        <v>7024911</v>
+        <v>7024692</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2720,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,12 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,56 +2749,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574670</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574677</v>
+        <v>135574634</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481568</v>
+        <v>481508</v>
       </c>
       <c r="R20" t="n">
-        <v>7024870</v>
+        <v>7024656</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2842,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2852,12 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,70 +2861,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574677</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574690</v>
+        <v>135574639</v>
       </c>
       <c r="B21" t="n">
-        <v>58086</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481438</v>
+        <v>481525</v>
       </c>
       <c r="R21" t="n">
-        <v>7024659</v>
+        <v>7024642</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2975,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,38 +2973,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574638</v>
+        <v>135574641</v>
       </c>
       <c r="B22" t="n">
-        <v>99210</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3052,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481544</v>
+        <v>481577</v>
       </c>
       <c r="R22" t="n">
-        <v>7024650</v>
+        <v>7024669</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3087,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3097,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3123,38 +3085,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574643</v>
+        <v>135574644</v>
       </c>
       <c r="B23" t="n">
-        <v>99210</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3126,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481579</v>
+        <v>481577</v>
       </c>
       <c r="R23" t="n">
-        <v>7024692</v>
+        <v>7024691</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3209,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3235,13 +3197,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574634</v>
+        <v>135574647</v>
       </c>
       <c r="B24" t="n">
         <v>99293</v>
@@ -3276,13 +3238,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481508</v>
+        <v>481595</v>
       </c>
       <c r="R24" t="n">
-        <v>7024656</v>
+        <v>7024696</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3311,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,13 +3309,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574639</v>
+        <v>135574648</v>
       </c>
       <c r="B25" t="n">
         <v>99293</v>
@@ -3388,13 +3350,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481525</v>
+        <v>481630</v>
       </c>
       <c r="R25" t="n">
-        <v>7024642</v>
+        <v>7024686</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3423,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,13 +3421,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574641</v>
+        <v>135574650</v>
       </c>
       <c r="B26" t="n">
         <v>99293</v>
@@ -3500,13 +3462,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481577</v>
+        <v>481647</v>
       </c>
       <c r="R26" t="n">
-        <v>7024669</v>
+        <v>7024696</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3535,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3545,7 +3507,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,13 +3538,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574644</v>
+        <v>135574651</v>
       </c>
       <c r="B27" t="n">
         <v>99293</v>
@@ -3612,13 +3579,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481577</v>
+        <v>481676</v>
       </c>
       <c r="R27" t="n">
-        <v>7024691</v>
+        <v>7024717</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3647,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3657,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,13 +3650,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574647</v>
+        <v>135574652</v>
       </c>
       <c r="B28" t="n">
         <v>99293</v>
@@ -3724,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481595</v>
+        <v>481695</v>
       </c>
       <c r="R28" t="n">
-        <v>7024696</v>
+        <v>7024735</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3759,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,13 +3762,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574648</v>
+        <v>135574655</v>
       </c>
       <c r="B29" t="n">
         <v>99293</v>
@@ -3836,10 +3803,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481630</v>
+        <v>481716</v>
       </c>
       <c r="R29" t="n">
-        <v>7024686</v>
+        <v>7024780</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3871,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,13 +3874,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574650</v>
+        <v>135574656</v>
       </c>
       <c r="B30" t="n">
         <v>99293</v>
@@ -3948,13 +3915,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481647</v>
+        <v>481734</v>
       </c>
       <c r="R30" t="n">
-        <v>7024696</v>
+        <v>7024791</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3983,7 +3950,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3993,12 +3960,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4024,13 +3986,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574651</v>
+        <v>135574660</v>
       </c>
       <c r="B31" t="n">
         <v>99293</v>
@@ -4065,13 +4027,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481676</v>
+        <v>481719</v>
       </c>
       <c r="R31" t="n">
-        <v>7024717</v>
+        <v>7024855</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4136,13 +4098,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574652</v>
+        <v>135574661</v>
       </c>
       <c r="B32" t="n">
         <v>99293</v>
@@ -4177,13 +4139,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481695</v>
+        <v>481701</v>
       </c>
       <c r="R32" t="n">
-        <v>7024735</v>
+        <v>7024856</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4212,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4222,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4248,13 +4210,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574655</v>
+        <v>135574663</v>
       </c>
       <c r="B33" t="n">
         <v>99293</v>
@@ -4289,13 +4251,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481716</v>
+        <v>481646</v>
       </c>
       <c r="R33" t="n">
-        <v>7024780</v>
+        <v>7024891</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4324,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4334,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,13 +4322,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574656</v>
+        <v>135574672</v>
       </c>
       <c r="B34" t="n">
         <v>99293</v>
@@ -4401,13 +4363,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481734</v>
+        <v>481561</v>
       </c>
       <c r="R34" t="n">
-        <v>7024791</v>
+        <v>7024902</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,13 +4434,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574660</v>
+        <v>135574674</v>
       </c>
       <c r="B35" t="n">
         <v>99293</v>
@@ -4513,13 +4475,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481719</v>
+        <v>481578</v>
       </c>
       <c r="R35" t="n">
-        <v>7024855</v>
+        <v>7024883</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4548,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4558,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4584,13 +4546,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574661</v>
+        <v>135574676</v>
       </c>
       <c r="B36" t="n">
         <v>99293</v>
@@ -4625,13 +4587,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481701</v>
+        <v>481552</v>
       </c>
       <c r="R36" t="n">
-        <v>7024856</v>
+        <v>7024876</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4660,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4670,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4696,13 +4658,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574663</v>
+        <v>135574680</v>
       </c>
       <c r="B37" t="n">
         <v>99293</v>
@@ -4737,13 +4699,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481646</v>
+        <v>481573</v>
       </c>
       <c r="R37" t="n">
-        <v>7024891</v>
+        <v>7024817</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4772,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4782,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4808,13 +4770,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574672</v>
+        <v>135574684</v>
       </c>
       <c r="B38" t="n">
         <v>99293</v>
@@ -4849,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481561</v>
+        <v>481498</v>
       </c>
       <c r="R38" t="n">
-        <v>7024902</v>
+        <v>7024750</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4884,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4894,7 +4856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4920,13 +4882,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574674</v>
+        <v>135574688</v>
       </c>
       <c r="B39" t="n">
         <v>99293</v>
@@ -4961,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481578</v>
+        <v>481456</v>
       </c>
       <c r="R39" t="n">
-        <v>7024883</v>
+        <v>7024666</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4996,7 +4958,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5006,7 +4968,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5032,13 +4994,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574676</v>
+        <v>135574689</v>
       </c>
       <c r="B40" t="n">
         <v>99293</v>
@@ -5073,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481552</v>
+        <v>481438</v>
       </c>
       <c r="R40" t="n">
-        <v>7024876</v>
+        <v>7024662</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5108,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5118,7 +5080,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,13 +5106,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574680</v>
+        <v>135574691</v>
       </c>
       <c r="B41" t="n">
         <v>99293</v>
@@ -5185,13 +5147,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481573</v>
+        <v>481402</v>
       </c>
       <c r="R41" t="n">
-        <v>7024817</v>
+        <v>7024646</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5220,7 +5182,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5230,7 +5192,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5256,13 +5218,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574684</v>
+        <v>135574692</v>
       </c>
       <c r="B42" t="n">
         <v>99293</v>
@@ -5297,13 +5259,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481498</v>
+        <v>481397</v>
       </c>
       <c r="R42" t="n">
-        <v>7024750</v>
+        <v>7024634</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5332,7 +5294,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5342,7 +5304,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5368,38 +5330,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574688</v>
+        <v>135574635</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>101502</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5409,10 +5371,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481456</v>
+        <v>481524</v>
       </c>
       <c r="R43" t="n">
-        <v>7024666</v>
+        <v>7024657</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5444,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5454,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,38 +5442,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574689</v>
+        <v>135574640</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>101502</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5521,13 +5483,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481438</v>
+        <v>481545</v>
       </c>
       <c r="R44" t="n">
-        <v>7024662</v>
+        <v>7024654</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5556,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5566,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5592,38 +5554,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574691</v>
+        <v>135574645</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>101502</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5633,13 +5595,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481402</v>
+        <v>481577</v>
       </c>
       <c r="R45" t="n">
-        <v>7024646</v>
+        <v>7024692</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5668,7 +5630,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5678,7 +5640,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5704,38 +5666,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574692</v>
+        <v>135574649</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>101502</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5745,13 +5707,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481397</v>
+        <v>481625</v>
       </c>
       <c r="R46" t="n">
-        <v>7024634</v>
+        <v>7024693</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5780,7 +5742,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5790,7 +5752,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,13 +5778,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574635</v>
+        <v>135574654</v>
       </c>
       <c r="B47" t="n">
         <v>101502</v>
@@ -5857,10 +5819,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481524</v>
+        <v>481705</v>
       </c>
       <c r="R47" t="n">
-        <v>7024657</v>
+        <v>7024756</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5892,7 +5854,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5902,7 +5864,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5928,13 +5890,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574640</v>
+        <v>135574657</v>
       </c>
       <c r="B48" t="n">
         <v>101502</v>
@@ -5969,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481545</v>
+        <v>481729</v>
       </c>
       <c r="R48" t="n">
-        <v>7024654</v>
+        <v>7024823</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6004,7 +5966,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6014,7 +5976,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6040,13 +6002,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574645</v>
+        <v>135574659</v>
       </c>
       <c r="B49" t="n">
         <v>101502</v>
@@ -6081,10 +6043,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481577</v>
+        <v>481714</v>
       </c>
       <c r="R49" t="n">
-        <v>7024692</v>
+        <v>7024855</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6116,7 +6078,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6126,7 +6088,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6152,13 +6114,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574649</v>
+        <v>135574667</v>
       </c>
       <c r="B50" t="n">
         <v>101502</v>
@@ -6193,10 +6155,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481625</v>
+        <v>481606</v>
       </c>
       <c r="R50" t="n">
-        <v>7024693</v>
+        <v>7024919</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6228,7 +6190,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6238,7 +6200,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,13 +6226,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574654</v>
+        <v>135574673</v>
       </c>
       <c r="B51" t="n">
         <v>101502</v>
@@ -6305,13 +6267,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481705</v>
+        <v>481558</v>
       </c>
       <c r="R51" t="n">
-        <v>7024756</v>
+        <v>7024899</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6340,7 +6302,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6350,7 +6312,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,13 +6338,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574673</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574657</v>
+        <v>135574678</v>
       </c>
       <c r="B52" t="n">
         <v>101502</v>
@@ -6417,10 +6379,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481729</v>
+        <v>481581</v>
       </c>
       <c r="R52" t="n">
-        <v>7024823</v>
+        <v>7024835</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6452,7 +6414,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6462,7 +6424,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6488,13 +6450,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574678</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574659</v>
+        <v>135574681</v>
       </c>
       <c r="B53" t="n">
         <v>101502</v>
@@ -6529,10 +6491,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481714</v>
+        <v>481566</v>
       </c>
       <c r="R53" t="n">
-        <v>7024855</v>
+        <v>7024806</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6564,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6574,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6600,13 +6562,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574681</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574667</v>
+        <v>135574685</v>
       </c>
       <c r="B54" t="n">
         <v>101502</v>
@@ -6641,13 +6603,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481606</v>
+        <v>481499</v>
       </c>
       <c r="R54" t="n">
-        <v>7024919</v>
+        <v>7024746</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6676,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6686,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6712,16 +6674,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574685</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574673</v>
+        <v>135574682</v>
       </c>
       <c r="B55" t="n">
-        <v>101502</v>
+        <v>99570</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6729,21 +6691,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>222812</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6753,13 +6715,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481558</v>
+        <v>481541</v>
       </c>
       <c r="R55" t="n">
-        <v>7024899</v>
+        <v>7024804</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6788,7 +6750,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6798,7 +6760,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6823,454 +6785,6 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135574678</v>
-      </c>
-      <c r="B56" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>481581</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7024835</v>
-      </c>
-      <c r="S56" t="n">
-        <v>4</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135574681</v>
-      </c>
-      <c r="B57" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>481566</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7024806</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135574685</v>
-      </c>
-      <c r="B58" t="n">
-        <v>101502</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>481499</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7024746</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135574682</v>
-      </c>
-      <c r="B59" t="n">
-        <v>99570</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>481541</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7024804</v>
-      </c>
-      <c r="S59" t="n">
-        <v>4</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -7332,10 +6846,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574690</v>
+        <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>58086</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,36 +2431,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481438</v>
+        <v>481606</v>
       </c>
       <c r="R17" t="n">
-        <v>7024659</v>
+        <v>7024919</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2487,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,54 +2518,59 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574666</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574638</v>
+        <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>99210</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481544</v>
+        <v>481600</v>
       </c>
       <c r="R18" t="n">
-        <v>7024650</v>
+        <v>7024916</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2609,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,54 +2640,58 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574668</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574643</v>
+        <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>99210</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481579</v>
+        <v>481586</v>
       </c>
       <c r="R19" t="n">
-        <v>7024692</v>
+        <v>7024911</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2713,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2730,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,51 +2761,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574670</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574634</v>
+        <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481508</v>
+        <v>481568</v>
       </c>
       <c r="R20" t="n">
-        <v>7024656</v>
+        <v>7024870</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2825,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2852,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,54 +2883,70 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574677</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574639</v>
+        <v>135574690</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>58086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481525</v>
+        <v>481438</v>
       </c>
       <c r="R21" t="n">
-        <v>7024642</v>
+        <v>7024659</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2937,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2985,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,38 +3011,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574641</v>
+        <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3052,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481577</v>
+        <v>481544</v>
       </c>
       <c r="R22" t="n">
-        <v>7024669</v>
+        <v>7024650</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3049,7 +3087,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3097,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,38 +3123,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574644</v>
+        <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481577</v>
+        <v>481579</v>
       </c>
       <c r="R23" t="n">
-        <v>7024691</v>
+        <v>7024692</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3161,7 +3199,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3209,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,13 +3235,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574647</v>
+        <v>135574634</v>
       </c>
       <c r="B24" t="n">
         <v>99293</v>
@@ -3238,13 +3276,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481595</v>
+        <v>481508</v>
       </c>
       <c r="R24" t="n">
-        <v>7024696</v>
+        <v>7024656</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3273,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,13 +3347,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574648</v>
+        <v>135574639</v>
       </c>
       <c r="B25" t="n">
         <v>99293</v>
@@ -3350,13 +3388,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481630</v>
+        <v>481525</v>
       </c>
       <c r="R25" t="n">
-        <v>7024686</v>
+        <v>7024642</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3385,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3433,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,13 +3459,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574650</v>
+        <v>135574641</v>
       </c>
       <c r="B26" t="n">
         <v>99293</v>
@@ -3462,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481647</v>
+        <v>481577</v>
       </c>
       <c r="R26" t="n">
-        <v>7024696</v>
+        <v>7024669</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3497,7 +3535,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,12 +3545,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,13 +3571,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574651</v>
+        <v>135574644</v>
       </c>
       <c r="B27" t="n">
         <v>99293</v>
@@ -3579,13 +3612,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481676</v>
+        <v>481577</v>
       </c>
       <c r="R27" t="n">
-        <v>7024717</v>
+        <v>7024691</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3614,7 +3647,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3657,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,13 +3683,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574652</v>
+        <v>135574647</v>
       </c>
       <c r="B28" t="n">
         <v>99293</v>
@@ -3691,13 +3724,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481695</v>
+        <v>481595</v>
       </c>
       <c r="R28" t="n">
-        <v>7024735</v>
+        <v>7024696</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3769,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574655</v>
+        <v>135574648</v>
       </c>
       <c r="B29" t="n">
         <v>99293</v>
@@ -3803,10 +3836,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481716</v>
+        <v>481630</v>
       </c>
       <c r="R29" t="n">
-        <v>7024780</v>
+        <v>7024686</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3838,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3881,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3874,13 +3907,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574656</v>
+        <v>135574650</v>
       </c>
       <c r="B30" t="n">
         <v>99293</v>
@@ -3915,13 +3948,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481734</v>
+        <v>481647</v>
       </c>
       <c r="R30" t="n">
-        <v>7024791</v>
+        <v>7024696</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3950,7 +3983,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3960,7 +3993,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,13 +4024,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574660</v>
+        <v>135574651</v>
       </c>
       <c r="B31" t="n">
         <v>99293</v>
@@ -4027,13 +4065,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481719</v>
+        <v>481676</v>
       </c>
       <c r="R31" t="n">
-        <v>7024855</v>
+        <v>7024717</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,7 +4100,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4110,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4098,13 +4136,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574661</v>
+        <v>135574652</v>
       </c>
       <c r="B32" t="n">
         <v>99293</v>
@@ -4139,13 +4177,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481701</v>
+        <v>481695</v>
       </c>
       <c r="R32" t="n">
-        <v>7024856</v>
+        <v>7024735</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4174,7 +4212,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +4222,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,13 +4248,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574663</v>
+        <v>135574655</v>
       </c>
       <c r="B33" t="n">
         <v>99293</v>
@@ -4251,13 +4289,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481646</v>
+        <v>481716</v>
       </c>
       <c r="R33" t="n">
-        <v>7024891</v>
+        <v>7024780</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4286,7 +4324,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4334,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,13 +4360,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574672</v>
+        <v>135574656</v>
       </c>
       <c r="B34" t="n">
         <v>99293</v>
@@ -4363,13 +4401,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481561</v>
+        <v>481734</v>
       </c>
       <c r="R34" t="n">
-        <v>7024902</v>
+        <v>7024791</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4398,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,13 +4472,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574674</v>
+        <v>135574660</v>
       </c>
       <c r="B35" t="n">
         <v>99293</v>
@@ -4475,13 +4513,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481578</v>
+        <v>481719</v>
       </c>
       <c r="R35" t="n">
-        <v>7024883</v>
+        <v>7024855</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4510,7 +4548,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4558,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,13 +4584,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574676</v>
+        <v>135574661</v>
       </c>
       <c r="B36" t="n">
         <v>99293</v>
@@ -4587,13 +4625,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481552</v>
+        <v>481701</v>
       </c>
       <c r="R36" t="n">
-        <v>7024876</v>
+        <v>7024856</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4622,7 +4660,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4670,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4658,13 +4696,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574680</v>
+        <v>135574663</v>
       </c>
       <c r="B37" t="n">
         <v>99293</v>
@@ -4699,13 +4737,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481573</v>
+        <v>481646</v>
       </c>
       <c r="R37" t="n">
-        <v>7024817</v>
+        <v>7024891</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4734,7 +4772,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4782,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4770,13 +4808,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574684</v>
+        <v>135574672</v>
       </c>
       <c r="B38" t="n">
         <v>99293</v>
@@ -4811,10 +4849,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481498</v>
+        <v>481561</v>
       </c>
       <c r="R38" t="n">
-        <v>7024750</v>
+        <v>7024902</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4846,7 +4884,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4894,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,13 +4920,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574688</v>
+        <v>135574674</v>
       </c>
       <c r="B39" t="n">
         <v>99293</v>
@@ -4923,10 +4961,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481456</v>
+        <v>481578</v>
       </c>
       <c r="R39" t="n">
-        <v>7024666</v>
+        <v>7024883</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4958,7 +4996,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +5006,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,13 +5032,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574689</v>
+        <v>135574676</v>
       </c>
       <c r="B40" t="n">
         <v>99293</v>
@@ -5035,10 +5073,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481438</v>
+        <v>481552</v>
       </c>
       <c r="R40" t="n">
-        <v>7024662</v>
+        <v>7024876</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5070,7 +5108,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +5118,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5106,13 +5144,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574691</v>
+        <v>135574680</v>
       </c>
       <c r="B41" t="n">
         <v>99293</v>
@@ -5147,13 +5185,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481402</v>
+        <v>481573</v>
       </c>
       <c r="R41" t="n">
-        <v>7024646</v>
+        <v>7024817</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,7 +5220,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5192,7 +5230,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5218,13 +5256,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574692</v>
+        <v>135574684</v>
       </c>
       <c r="B42" t="n">
         <v>99293</v>
@@ -5259,13 +5297,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481397</v>
+        <v>481498</v>
       </c>
       <c r="R42" t="n">
-        <v>7024634</v>
+        <v>7024750</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5294,7 +5332,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5304,7 +5342,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,38 +5368,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574635</v>
+        <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>101502</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5409,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481524</v>
+        <v>481456</v>
       </c>
       <c r="R43" t="n">
-        <v>7024657</v>
+        <v>7024666</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5406,7 +5444,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5454,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5442,38 +5480,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574640</v>
+        <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>101502</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,13 +5521,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481545</v>
+        <v>481438</v>
       </c>
       <c r="R44" t="n">
-        <v>7024654</v>
+        <v>7024662</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5518,7 +5556,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5566,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5554,38 +5592,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574645</v>
+        <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>101502</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,13 +5633,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481577</v>
+        <v>481402</v>
       </c>
       <c r="R45" t="n">
-        <v>7024692</v>
+        <v>7024646</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5630,7 +5668,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5640,7 +5678,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,38 +5704,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574649</v>
+        <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>101502</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5707,13 +5745,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481625</v>
+        <v>481397</v>
       </c>
       <c r="R46" t="n">
-        <v>7024693</v>
+        <v>7024634</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5742,7 +5780,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5752,7 +5790,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,13 +5816,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574654</v>
+        <v>135574635</v>
       </c>
       <c r="B47" t="n">
         <v>101502</v>
@@ -5819,10 +5857,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481705</v>
+        <v>481524</v>
       </c>
       <c r="R47" t="n">
-        <v>7024756</v>
+        <v>7024657</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5854,7 +5892,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5864,7 +5902,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5890,13 +5928,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574657</v>
+        <v>135574640</v>
       </c>
       <c r="B48" t="n">
         <v>101502</v>
@@ -5931,10 +5969,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481729</v>
+        <v>481545</v>
       </c>
       <c r="R48" t="n">
-        <v>7024823</v>
+        <v>7024654</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5966,7 +6004,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5976,7 +6014,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6002,13 +6040,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574659</v>
+        <v>135574645</v>
       </c>
       <c r="B49" t="n">
         <v>101502</v>
@@ -6043,10 +6081,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481714</v>
+        <v>481577</v>
       </c>
       <c r="R49" t="n">
-        <v>7024855</v>
+        <v>7024692</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6078,7 +6116,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6088,7 +6126,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6114,13 +6152,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574667</v>
+        <v>135574649</v>
       </c>
       <c r="B50" t="n">
         <v>101502</v>
@@ -6155,10 +6193,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481606</v>
+        <v>481625</v>
       </c>
       <c r="R50" t="n">
-        <v>7024919</v>
+        <v>7024693</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6190,7 +6228,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6200,7 +6238,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6226,13 +6264,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574673</v>
+        <v>135574654</v>
       </c>
       <c r="B51" t="n">
         <v>101502</v>
@@ -6267,13 +6305,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481558</v>
+        <v>481705</v>
       </c>
       <c r="R51" t="n">
-        <v>7024899</v>
+        <v>7024756</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6302,7 +6340,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6312,7 +6350,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6338,13 +6376,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574678</v>
+        <v>135574657</v>
       </c>
       <c r="B52" t="n">
         <v>101502</v>
@@ -6379,10 +6417,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481581</v>
+        <v>481729</v>
       </c>
       <c r="R52" t="n">
-        <v>7024835</v>
+        <v>7024823</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6414,7 +6452,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6424,7 +6462,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6450,13 +6488,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574681</v>
+        <v>135574659</v>
       </c>
       <c r="B53" t="n">
         <v>101502</v>
@@ -6491,10 +6529,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481566</v>
+        <v>481714</v>
       </c>
       <c r="R53" t="n">
-        <v>7024806</v>
+        <v>7024855</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6526,7 +6564,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6574,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6562,13 +6600,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574685</v>
+        <v>135574667</v>
       </c>
       <c r="B54" t="n">
         <v>101502</v>
@@ -6603,13 +6641,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481499</v>
+        <v>481606</v>
       </c>
       <c r="R54" t="n">
-        <v>7024746</v>
+        <v>7024919</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6638,7 +6676,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6686,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6674,16 +6712,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574682</v>
+        <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>99570</v>
+        <v>101502</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6691,21 +6729,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,13 +6753,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481541</v>
+        <v>481558</v>
       </c>
       <c r="R55" t="n">
-        <v>7024804</v>
+        <v>7024899</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6750,7 +6788,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6760,7 +6798,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6785,6 +6823,454 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574673</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135574678</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>481581</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7024835</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574678</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135574681</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>481566</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7024806</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574681</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135574685</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>481499</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7024746</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574685</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135574682</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>481541</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7024804</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -6846,6 +7332,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135574675</v>
       </c>
       <c r="B2" t="n">
-        <v>92897</v>
+        <v>92898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135574646</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135574683</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135574630</v>
       </c>
       <c r="B5" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135574631</v>
       </c>
       <c r="B6" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135574632</v>
       </c>
       <c r="B7" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135574633</v>
       </c>
       <c r="B8" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135574636</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>135574637</v>
       </c>
       <c r="B10" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135574642</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135574658</v>
       </c>
       <c r="B12" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135574662</v>
       </c>
       <c r="B13" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135574686</v>
       </c>
       <c r="B14" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135574687</v>
       </c>
       <c r="B15" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>135574634</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>135574639</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>135574641</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>135574644</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>135574647</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>135574648</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>135574650</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135574651</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135574652</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135574655</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135574656</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135574660</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135574661</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135574663</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135574672</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135574674</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135574676</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135574680</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135574684</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135574635</v>
       </c>
       <c r="B47" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>135574640</v>
       </c>
       <c r="B48" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>135574645</v>
       </c>
       <c r="B49" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>135574649</v>
       </c>
       <c r="B50" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>135574654</v>
       </c>
       <c r="B51" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135574657</v>
       </c>
       <c r="B52" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>135574659</v>
       </c>
       <c r="B53" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>135574667</v>
       </c>
       <c r="B54" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>135574678</v>
       </c>
       <c r="B56" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>135574681</v>
       </c>
       <c r="B57" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>135574685</v>
       </c>
       <c r="B58" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>135574682</v>
       </c>
       <c r="B59" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135574675</v>
       </c>
       <c r="B2" t="n">
-        <v>92898</v>
+        <v>92899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574666</v>
+        <v>135574690</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>58086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,24 +2431,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481606</v>
+        <v>481438</v>
       </c>
       <c r="R17" t="n">
-        <v>7024919</v>
+        <v>7024659</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,12 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,59 +2525,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574666</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574668</v>
+        <v>135574638</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>99212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481600</v>
+        <v>481544</v>
       </c>
       <c r="R18" t="n">
-        <v>7024916</v>
+        <v>7024650</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2599,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,12 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,58 +2637,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574668</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574670</v>
+        <v>135574643</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>99212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481586</v>
+        <v>481579</v>
       </c>
       <c r="R19" t="n">
-        <v>7024911</v>
+        <v>7024692</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2720,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,12 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,56 +2749,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574670</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574677</v>
+        <v>135574634</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481568</v>
+        <v>481508</v>
       </c>
       <c r="R20" t="n">
-        <v>7024870</v>
+        <v>7024656</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2842,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2852,12 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,70 +2861,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574677</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574690</v>
+        <v>135574639</v>
       </c>
       <c r="B21" t="n">
-        <v>58086</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481438</v>
+        <v>481525</v>
       </c>
       <c r="R21" t="n">
-        <v>7024659</v>
+        <v>7024642</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2975,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,38 +2973,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574638</v>
+        <v>135574641</v>
       </c>
       <c r="B22" t="n">
-        <v>99211</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3052,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481544</v>
+        <v>481577</v>
       </c>
       <c r="R22" t="n">
-        <v>7024650</v>
+        <v>7024669</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3087,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3097,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3123,38 +3085,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574643</v>
+        <v>135574644</v>
       </c>
       <c r="B23" t="n">
-        <v>99211</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3126,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481579</v>
+        <v>481577</v>
       </c>
       <c r="R23" t="n">
-        <v>7024692</v>
+        <v>7024691</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3209,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3235,16 +3197,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574634</v>
+        <v>135574647</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,13 +3238,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481508</v>
+        <v>481595</v>
       </c>
       <c r="R24" t="n">
-        <v>7024656</v>
+        <v>7024696</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3311,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,16 +3309,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574639</v>
+        <v>135574648</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,13 +3350,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481525</v>
+        <v>481630</v>
       </c>
       <c r="R25" t="n">
-        <v>7024642</v>
+        <v>7024686</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3423,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,16 +3421,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574641</v>
+        <v>135574650</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,13 +3462,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481577</v>
+        <v>481647</v>
       </c>
       <c r="R26" t="n">
-        <v>7024669</v>
+        <v>7024696</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3535,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3545,7 +3507,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,16 +3538,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574644</v>
+        <v>135574651</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,13 +3579,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481577</v>
+        <v>481676</v>
       </c>
       <c r="R27" t="n">
-        <v>7024691</v>
+        <v>7024717</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3647,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3657,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,16 +3650,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574647</v>
+        <v>135574652</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481595</v>
+        <v>481695</v>
       </c>
       <c r="R28" t="n">
-        <v>7024696</v>
+        <v>7024735</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3759,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,16 +3762,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574648</v>
+        <v>135574655</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,10 +3803,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481630</v>
+        <v>481716</v>
       </c>
       <c r="R29" t="n">
-        <v>7024686</v>
+        <v>7024780</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3871,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,16 +3874,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574650</v>
+        <v>135574656</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,13 +3915,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481647</v>
+        <v>481734</v>
       </c>
       <c r="R30" t="n">
-        <v>7024696</v>
+        <v>7024791</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3983,7 +3950,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3993,12 +3960,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4024,16 +3986,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574651</v>
+        <v>135574660</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,13 +4027,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481676</v>
+        <v>481719</v>
       </c>
       <c r="R31" t="n">
-        <v>7024717</v>
+        <v>7024855</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4136,16 +4098,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574652</v>
+        <v>135574661</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4177,13 +4139,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481695</v>
+        <v>481701</v>
       </c>
       <c r="R32" t="n">
-        <v>7024735</v>
+        <v>7024856</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4212,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4222,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4248,16 +4210,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574655</v>
+        <v>135574663</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4289,13 +4251,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481716</v>
+        <v>481646</v>
       </c>
       <c r="R33" t="n">
-        <v>7024780</v>
+        <v>7024891</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4324,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4334,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,16 +4322,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574656</v>
+        <v>135574672</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4401,13 +4363,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481734</v>
+        <v>481561</v>
       </c>
       <c r="R34" t="n">
-        <v>7024791</v>
+        <v>7024902</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,16 +4434,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574660</v>
+        <v>135574674</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,13 +4475,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481719</v>
+        <v>481578</v>
       </c>
       <c r="R35" t="n">
-        <v>7024855</v>
+        <v>7024883</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4548,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4558,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4584,16 +4546,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574661</v>
+        <v>135574676</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,13 +4587,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481701</v>
+        <v>481552</v>
       </c>
       <c r="R36" t="n">
-        <v>7024856</v>
+        <v>7024876</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4660,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4670,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4696,16 +4658,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574663</v>
+        <v>135574680</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,13 +4699,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481646</v>
+        <v>481573</v>
       </c>
       <c r="R37" t="n">
-        <v>7024891</v>
+        <v>7024817</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4772,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4782,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4808,16 +4770,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574672</v>
+        <v>135574684</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4849,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481561</v>
+        <v>481498</v>
       </c>
       <c r="R38" t="n">
-        <v>7024902</v>
+        <v>7024750</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4884,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4894,7 +4856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4920,16 +4882,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574674</v>
+        <v>135574688</v>
       </c>
       <c r="B39" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4961,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481578</v>
+        <v>481456</v>
       </c>
       <c r="R39" t="n">
-        <v>7024883</v>
+        <v>7024666</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4996,7 +4958,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5006,7 +4968,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5032,16 +4994,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574676</v>
+        <v>135574689</v>
       </c>
       <c r="B40" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5073,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481552</v>
+        <v>481438</v>
       </c>
       <c r="R40" t="n">
-        <v>7024876</v>
+        <v>7024662</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5108,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5118,7 +5080,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,16 +5106,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574680</v>
+        <v>135574691</v>
       </c>
       <c r="B41" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5185,13 +5147,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481573</v>
+        <v>481402</v>
       </c>
       <c r="R41" t="n">
-        <v>7024817</v>
+        <v>7024646</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5220,7 +5182,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5230,7 +5192,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5256,16 +5218,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574684</v>
+        <v>135574692</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5297,13 +5259,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481498</v>
+        <v>481397</v>
       </c>
       <c r="R42" t="n">
-        <v>7024750</v>
+        <v>7024634</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5332,7 +5294,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5342,7 +5304,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5368,38 +5330,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574688</v>
+        <v>135574635</v>
       </c>
       <c r="B43" t="n">
-        <v>99294</v>
+        <v>101505</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5409,10 +5371,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481456</v>
+        <v>481524</v>
       </c>
       <c r="R43" t="n">
-        <v>7024666</v>
+        <v>7024657</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5444,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5454,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,38 +5442,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574689</v>
+        <v>135574640</v>
       </c>
       <c r="B44" t="n">
-        <v>99294</v>
+        <v>101505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5521,13 +5483,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481438</v>
+        <v>481545</v>
       </c>
       <c r="R44" t="n">
-        <v>7024662</v>
+        <v>7024654</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5556,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5566,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5592,38 +5554,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574691</v>
+        <v>135574645</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>101505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5633,13 +5595,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481402</v>
+        <v>481577</v>
       </c>
       <c r="R45" t="n">
-        <v>7024646</v>
+        <v>7024692</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5668,7 +5630,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5678,7 +5640,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5704,38 +5666,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574692</v>
+        <v>135574649</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>101505</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5745,13 +5707,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481397</v>
+        <v>481625</v>
       </c>
       <c r="R46" t="n">
-        <v>7024634</v>
+        <v>7024693</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5780,7 +5742,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5790,7 +5752,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,16 +5778,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574635</v>
+        <v>135574654</v>
       </c>
       <c r="B47" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5857,10 +5819,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481524</v>
+        <v>481705</v>
       </c>
       <c r="R47" t="n">
-        <v>7024657</v>
+        <v>7024756</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5892,7 +5854,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5902,7 +5864,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5928,16 +5890,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574640</v>
+        <v>135574657</v>
       </c>
       <c r="B48" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5969,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481545</v>
+        <v>481729</v>
       </c>
       <c r="R48" t="n">
-        <v>7024654</v>
+        <v>7024823</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6004,7 +5966,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6014,7 +5976,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6040,16 +6002,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574645</v>
+        <v>135574659</v>
       </c>
       <c r="B49" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6081,10 +6043,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481577</v>
+        <v>481714</v>
       </c>
       <c r="R49" t="n">
-        <v>7024692</v>
+        <v>7024855</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6116,7 +6078,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6126,7 +6088,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6152,16 +6114,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574649</v>
+        <v>135574667</v>
       </c>
       <c r="B50" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6193,10 +6155,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481625</v>
+        <v>481606</v>
       </c>
       <c r="R50" t="n">
-        <v>7024693</v>
+        <v>7024919</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6228,7 +6190,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6238,7 +6200,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,16 +6226,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574654</v>
+        <v>135574673</v>
       </c>
       <c r="B51" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6305,13 +6267,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481705</v>
+        <v>481558</v>
       </c>
       <c r="R51" t="n">
-        <v>7024756</v>
+        <v>7024899</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6340,7 +6302,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6350,7 +6312,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,16 +6338,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574673</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574657</v>
+        <v>135574678</v>
       </c>
       <c r="B52" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6417,10 +6379,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481729</v>
+        <v>481581</v>
       </c>
       <c r="R52" t="n">
-        <v>7024823</v>
+        <v>7024835</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6452,7 +6414,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6462,7 +6424,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6488,16 +6450,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574678</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574659</v>
+        <v>135574681</v>
       </c>
       <c r="B53" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6529,10 +6491,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481714</v>
+        <v>481566</v>
       </c>
       <c r="R53" t="n">
-        <v>7024855</v>
+        <v>7024806</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6564,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6574,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6600,16 +6562,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574681</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574667</v>
+        <v>135574685</v>
       </c>
       <c r="B54" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6641,13 +6603,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481606</v>
+        <v>481499</v>
       </c>
       <c r="R54" t="n">
-        <v>7024919</v>
+        <v>7024746</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6676,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6686,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6712,16 +6674,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574685</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574673</v>
+        <v>135574682</v>
       </c>
       <c r="B55" t="n">
-        <v>101504</v>
+        <v>99572</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6729,21 +6691,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>222812</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6753,13 +6715,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481558</v>
+        <v>481541</v>
       </c>
       <c r="R55" t="n">
-        <v>7024899</v>
+        <v>7024804</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6788,7 +6750,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6798,7 +6760,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6823,454 +6785,6 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135574678</v>
-      </c>
-      <c r="B56" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>481581</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7024835</v>
-      </c>
-      <c r="S56" t="n">
-        <v>4</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135574681</v>
-      </c>
-      <c r="B57" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>481566</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7024806</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135574685</v>
-      </c>
-      <c r="B58" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>481499</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7024746</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135574682</v>
-      </c>
-      <c r="B59" t="n">
-        <v>99571</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>481541</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7024804</v>
-      </c>
-      <c r="S59" t="n">
-        <v>4</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -7332,10 +6846,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574690</v>
+        <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>58086</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,36 +2431,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481438</v>
+        <v>481606</v>
       </c>
       <c r="R17" t="n">
-        <v>7024659</v>
+        <v>7024919</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2487,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,54 +2518,59 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574666</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574638</v>
+        <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>99212</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481544</v>
+        <v>481600</v>
       </c>
       <c r="R18" t="n">
-        <v>7024650</v>
+        <v>7024916</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2609,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,54 +2640,58 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574668</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574643</v>
+        <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>99212</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481579</v>
+        <v>481586</v>
       </c>
       <c r="R19" t="n">
-        <v>7024692</v>
+        <v>7024911</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2713,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2730,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,51 +2761,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574670</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574634</v>
+        <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481508</v>
+        <v>481568</v>
       </c>
       <c r="R20" t="n">
-        <v>7024656</v>
+        <v>7024870</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2825,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2852,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,54 +2883,70 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574677</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574639</v>
+        <v>135574690</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>58086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481525</v>
+        <v>481438</v>
       </c>
       <c r="R21" t="n">
-        <v>7024642</v>
+        <v>7024659</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2937,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2985,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,38 +3011,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574641</v>
+        <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3052,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481577</v>
+        <v>481544</v>
       </c>
       <c r="R22" t="n">
-        <v>7024669</v>
+        <v>7024650</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3049,7 +3087,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3097,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,38 +3123,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574644</v>
+        <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481577</v>
+        <v>481579</v>
       </c>
       <c r="R23" t="n">
-        <v>7024691</v>
+        <v>7024692</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3161,7 +3199,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3209,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,13 +3235,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574647</v>
+        <v>135574634</v>
       </c>
       <c r="B24" t="n">
         <v>99295</v>
@@ -3238,13 +3276,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481595</v>
+        <v>481508</v>
       </c>
       <c r="R24" t="n">
-        <v>7024696</v>
+        <v>7024656</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3273,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,13 +3347,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574648</v>
+        <v>135574639</v>
       </c>
       <c r="B25" t="n">
         <v>99295</v>
@@ -3350,13 +3388,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481630</v>
+        <v>481525</v>
       </c>
       <c r="R25" t="n">
-        <v>7024686</v>
+        <v>7024642</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3385,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3433,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,13 +3459,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574650</v>
+        <v>135574641</v>
       </c>
       <c r="B26" t="n">
         <v>99295</v>
@@ -3462,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481647</v>
+        <v>481577</v>
       </c>
       <c r="R26" t="n">
-        <v>7024696</v>
+        <v>7024669</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3497,7 +3535,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,12 +3545,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,13 +3571,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574651</v>
+        <v>135574644</v>
       </c>
       <c r="B27" t="n">
         <v>99295</v>
@@ -3579,13 +3612,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481676</v>
+        <v>481577</v>
       </c>
       <c r="R27" t="n">
-        <v>7024717</v>
+        <v>7024691</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3614,7 +3647,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3657,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,13 +3683,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574652</v>
+        <v>135574647</v>
       </c>
       <c r="B28" t="n">
         <v>99295</v>
@@ -3691,13 +3724,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481695</v>
+        <v>481595</v>
       </c>
       <c r="R28" t="n">
-        <v>7024735</v>
+        <v>7024696</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3769,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574655</v>
+        <v>135574648</v>
       </c>
       <c r="B29" t="n">
         <v>99295</v>
@@ -3803,10 +3836,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481716</v>
+        <v>481630</v>
       </c>
       <c r="R29" t="n">
-        <v>7024780</v>
+        <v>7024686</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3838,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3881,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3874,13 +3907,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574656</v>
+        <v>135574650</v>
       </c>
       <c r="B30" t="n">
         <v>99295</v>
@@ -3915,13 +3948,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481734</v>
+        <v>481647</v>
       </c>
       <c r="R30" t="n">
-        <v>7024791</v>
+        <v>7024696</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3950,7 +3983,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3960,7 +3993,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,13 +4024,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574660</v>
+        <v>135574651</v>
       </c>
       <c r="B31" t="n">
         <v>99295</v>
@@ -4027,13 +4065,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481719</v>
+        <v>481676</v>
       </c>
       <c r="R31" t="n">
-        <v>7024855</v>
+        <v>7024717</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,7 +4100,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4110,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4098,13 +4136,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574661</v>
+        <v>135574652</v>
       </c>
       <c r="B32" t="n">
         <v>99295</v>
@@ -4139,13 +4177,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481701</v>
+        <v>481695</v>
       </c>
       <c r="R32" t="n">
-        <v>7024856</v>
+        <v>7024735</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4174,7 +4212,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +4222,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,13 +4248,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574663</v>
+        <v>135574655</v>
       </c>
       <c r="B33" t="n">
         <v>99295</v>
@@ -4251,13 +4289,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481646</v>
+        <v>481716</v>
       </c>
       <c r="R33" t="n">
-        <v>7024891</v>
+        <v>7024780</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4286,7 +4324,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4334,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,13 +4360,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574672</v>
+        <v>135574656</v>
       </c>
       <c r="B34" t="n">
         <v>99295</v>
@@ -4363,13 +4401,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481561</v>
+        <v>481734</v>
       </c>
       <c r="R34" t="n">
-        <v>7024902</v>
+        <v>7024791</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4398,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,13 +4472,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574674</v>
+        <v>135574660</v>
       </c>
       <c r="B35" t="n">
         <v>99295</v>
@@ -4475,13 +4513,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481578</v>
+        <v>481719</v>
       </c>
       <c r="R35" t="n">
-        <v>7024883</v>
+        <v>7024855</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4510,7 +4548,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4558,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,13 +4584,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574676</v>
+        <v>135574661</v>
       </c>
       <c r="B36" t="n">
         <v>99295</v>
@@ -4587,13 +4625,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481552</v>
+        <v>481701</v>
       </c>
       <c r="R36" t="n">
-        <v>7024876</v>
+        <v>7024856</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4622,7 +4660,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4670,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4658,13 +4696,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574680</v>
+        <v>135574663</v>
       </c>
       <c r="B37" t="n">
         <v>99295</v>
@@ -4699,13 +4737,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481573</v>
+        <v>481646</v>
       </c>
       <c r="R37" t="n">
-        <v>7024817</v>
+        <v>7024891</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4734,7 +4772,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4782,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4770,13 +4808,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574684</v>
+        <v>135574672</v>
       </c>
       <c r="B38" t="n">
         <v>99295</v>
@@ -4811,10 +4849,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481498</v>
+        <v>481561</v>
       </c>
       <c r="R38" t="n">
-        <v>7024750</v>
+        <v>7024902</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4846,7 +4884,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4894,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,13 +4920,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574688</v>
+        <v>135574674</v>
       </c>
       <c r="B39" t="n">
         <v>99295</v>
@@ -4923,10 +4961,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481456</v>
+        <v>481578</v>
       </c>
       <c r="R39" t="n">
-        <v>7024666</v>
+        <v>7024883</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4958,7 +4996,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +5006,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,13 +5032,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574689</v>
+        <v>135574676</v>
       </c>
       <c r="B40" t="n">
         <v>99295</v>
@@ -5035,10 +5073,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481438</v>
+        <v>481552</v>
       </c>
       <c r="R40" t="n">
-        <v>7024662</v>
+        <v>7024876</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5070,7 +5108,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +5118,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5106,13 +5144,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574691</v>
+        <v>135574680</v>
       </c>
       <c r="B41" t="n">
         <v>99295</v>
@@ -5147,13 +5185,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481402</v>
+        <v>481573</v>
       </c>
       <c r="R41" t="n">
-        <v>7024646</v>
+        <v>7024817</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,7 +5220,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5192,7 +5230,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5218,13 +5256,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574692</v>
+        <v>135574684</v>
       </c>
       <c r="B42" t="n">
         <v>99295</v>
@@ -5259,13 +5297,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481397</v>
+        <v>481498</v>
       </c>
       <c r="R42" t="n">
-        <v>7024634</v>
+        <v>7024750</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5294,7 +5332,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5304,7 +5342,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,38 +5368,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574635</v>
+        <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5409,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481524</v>
+        <v>481456</v>
       </c>
       <c r="R43" t="n">
-        <v>7024657</v>
+        <v>7024666</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5406,7 +5444,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5454,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5442,38 +5480,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574640</v>
+        <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,13 +5521,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481545</v>
+        <v>481438</v>
       </c>
       <c r="R44" t="n">
-        <v>7024654</v>
+        <v>7024662</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5518,7 +5556,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5566,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5554,38 +5592,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574645</v>
+        <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,13 +5633,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481577</v>
+        <v>481402</v>
       </c>
       <c r="R45" t="n">
-        <v>7024692</v>
+        <v>7024646</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5630,7 +5668,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5640,7 +5678,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,38 +5704,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574649</v>
+        <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5707,13 +5745,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481625</v>
+        <v>481397</v>
       </c>
       <c r="R46" t="n">
-        <v>7024693</v>
+        <v>7024634</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5742,7 +5780,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5752,7 +5790,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,13 +5816,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574654</v>
+        <v>135574635</v>
       </c>
       <c r="B47" t="n">
         <v>101505</v>
@@ -5819,10 +5857,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481705</v>
+        <v>481524</v>
       </c>
       <c r="R47" t="n">
-        <v>7024756</v>
+        <v>7024657</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5854,7 +5892,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5864,7 +5902,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5890,13 +5928,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574657</v>
+        <v>135574640</v>
       </c>
       <c r="B48" t="n">
         <v>101505</v>
@@ -5931,10 +5969,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481729</v>
+        <v>481545</v>
       </c>
       <c r="R48" t="n">
-        <v>7024823</v>
+        <v>7024654</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5966,7 +6004,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5976,7 +6014,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6002,13 +6040,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574659</v>
+        <v>135574645</v>
       </c>
       <c r="B49" t="n">
         <v>101505</v>
@@ -6043,10 +6081,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481714</v>
+        <v>481577</v>
       </c>
       <c r="R49" t="n">
-        <v>7024855</v>
+        <v>7024692</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6078,7 +6116,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6088,7 +6126,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6114,13 +6152,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574667</v>
+        <v>135574649</v>
       </c>
       <c r="B50" t="n">
         <v>101505</v>
@@ -6155,10 +6193,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481606</v>
+        <v>481625</v>
       </c>
       <c r="R50" t="n">
-        <v>7024919</v>
+        <v>7024693</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6190,7 +6228,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6200,7 +6238,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6226,13 +6264,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574673</v>
+        <v>135574654</v>
       </c>
       <c r="B51" t="n">
         <v>101505</v>
@@ -6267,13 +6305,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481558</v>
+        <v>481705</v>
       </c>
       <c r="R51" t="n">
-        <v>7024899</v>
+        <v>7024756</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6302,7 +6340,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6312,7 +6350,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6338,13 +6376,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574678</v>
+        <v>135574657</v>
       </c>
       <c r="B52" t="n">
         <v>101505</v>
@@ -6379,10 +6417,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481581</v>
+        <v>481729</v>
       </c>
       <c r="R52" t="n">
-        <v>7024835</v>
+        <v>7024823</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6414,7 +6452,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6424,7 +6462,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6450,13 +6488,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574681</v>
+        <v>135574659</v>
       </c>
       <c r="B53" t="n">
         <v>101505</v>
@@ -6491,10 +6529,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481566</v>
+        <v>481714</v>
       </c>
       <c r="R53" t="n">
-        <v>7024806</v>
+        <v>7024855</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6526,7 +6564,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6574,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6562,13 +6600,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574685</v>
+        <v>135574667</v>
       </c>
       <c r="B54" t="n">
         <v>101505</v>
@@ -6603,13 +6641,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481499</v>
+        <v>481606</v>
       </c>
       <c r="R54" t="n">
-        <v>7024746</v>
+        <v>7024919</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6638,7 +6676,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6686,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6674,16 +6712,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574682</v>
+        <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>99572</v>
+        <v>101505</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6691,21 +6729,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,13 +6753,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481541</v>
+        <v>481558</v>
       </c>
       <c r="R55" t="n">
-        <v>7024804</v>
+        <v>7024899</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6750,7 +6788,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6760,7 +6798,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6785,6 +6823,454 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574673</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135574678</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>481581</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7024835</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574678</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135574681</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>481566</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7024806</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574681</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135574685</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>481499</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7024746</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574685</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135574682</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99572</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>481541</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7024804</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -6846,6 +7332,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -2406,7 +2406,7 @@
         <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -2406,7 +2406,7 @@
         <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -2406,7 +2406,7 @@
         <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -2406,7 +2406,7 @@
         <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574666</v>
+        <v>135574690</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,24 +2431,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481606</v>
+        <v>481438</v>
       </c>
       <c r="R17" t="n">
-        <v>7024919</v>
+        <v>7024659</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,12 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,59 +2525,54 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574666</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574668</v>
+        <v>135574638</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>99212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481600</v>
+        <v>481544</v>
       </c>
       <c r="R18" t="n">
-        <v>7024916</v>
+        <v>7024650</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2599,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,12 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,58 +2637,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574668</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574670</v>
+        <v>135574643</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>99212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481586</v>
+        <v>481579</v>
       </c>
       <c r="R19" t="n">
-        <v>7024911</v>
+        <v>7024692</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2720,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,12 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,56 +2749,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574670</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574677</v>
+        <v>135574634</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481568</v>
+        <v>481508</v>
       </c>
       <c r="R20" t="n">
-        <v>7024870</v>
+        <v>7024656</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2842,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2852,12 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,70 +2861,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574677</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574690</v>
+        <v>135574639</v>
       </c>
       <c r="B21" t="n">
-        <v>58086</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481438</v>
+        <v>481525</v>
       </c>
       <c r="R21" t="n">
-        <v>7024659</v>
+        <v>7024642</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2975,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2985,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,38 +2973,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574638</v>
+        <v>135574641</v>
       </c>
       <c r="B22" t="n">
-        <v>99212</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3052,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481544</v>
+        <v>481577</v>
       </c>
       <c r="R22" t="n">
-        <v>7024650</v>
+        <v>7024669</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3087,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3097,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3123,38 +3085,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574643</v>
+        <v>135574644</v>
       </c>
       <c r="B23" t="n">
-        <v>99212</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,13 +3126,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481579</v>
+        <v>481577</v>
       </c>
       <c r="R23" t="n">
-        <v>7024692</v>
+        <v>7024691</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3199,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3209,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3235,13 +3197,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574634</v>
+        <v>135574647</v>
       </c>
       <c r="B24" t="n">
         <v>99295</v>
@@ -3276,13 +3238,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481508</v>
+        <v>481595</v>
       </c>
       <c r="R24" t="n">
-        <v>7024656</v>
+        <v>7024696</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3311,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3321,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,13 +3309,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574639</v>
+        <v>135574648</v>
       </c>
       <c r="B25" t="n">
         <v>99295</v>
@@ -3388,13 +3350,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481525</v>
+        <v>481630</v>
       </c>
       <c r="R25" t="n">
-        <v>7024642</v>
+        <v>7024686</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3423,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3433,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3459,13 +3421,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574641</v>
+        <v>135574650</v>
       </c>
       <c r="B26" t="n">
         <v>99295</v>
@@ -3500,13 +3462,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481577</v>
+        <v>481647</v>
       </c>
       <c r="R26" t="n">
-        <v>7024669</v>
+        <v>7024696</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3535,7 +3497,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3545,7 +3507,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,13 +3538,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574644</v>
+        <v>135574651</v>
       </c>
       <c r="B27" t="n">
         <v>99295</v>
@@ -3612,13 +3579,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481577</v>
+        <v>481676</v>
       </c>
       <c r="R27" t="n">
-        <v>7024691</v>
+        <v>7024717</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3647,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3657,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,13 +3650,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574647</v>
+        <v>135574652</v>
       </c>
       <c r="B28" t="n">
         <v>99295</v>
@@ -3724,13 +3691,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481595</v>
+        <v>481695</v>
       </c>
       <c r="R28" t="n">
-        <v>7024696</v>
+        <v>7024735</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3759,7 +3726,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,7 +3736,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,13 +3762,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574648</v>
+        <v>135574655</v>
       </c>
       <c r="B29" t="n">
         <v>99295</v>
@@ -3836,10 +3803,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481630</v>
+        <v>481716</v>
       </c>
       <c r="R29" t="n">
-        <v>7024686</v>
+        <v>7024780</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3871,7 +3838,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,7 +3848,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,13 +3874,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574650</v>
+        <v>135574656</v>
       </c>
       <c r="B30" t="n">
         <v>99295</v>
@@ -3948,13 +3915,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481647</v>
+        <v>481734</v>
       </c>
       <c r="R30" t="n">
-        <v>7024696</v>
+        <v>7024791</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3983,7 +3950,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3993,12 +3960,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4024,13 +3986,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574651</v>
+        <v>135574660</v>
       </c>
       <c r="B31" t="n">
         <v>99295</v>
@@ -4065,13 +4027,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481676</v>
+        <v>481719</v>
       </c>
       <c r="R31" t="n">
-        <v>7024717</v>
+        <v>7024855</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4100,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4110,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4136,13 +4098,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574652</v>
+        <v>135574661</v>
       </c>
       <c r="B32" t="n">
         <v>99295</v>
@@ -4177,13 +4139,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481695</v>
+        <v>481701</v>
       </c>
       <c r="R32" t="n">
-        <v>7024735</v>
+        <v>7024856</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4212,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4222,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4248,13 +4210,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574655</v>
+        <v>135574663</v>
       </c>
       <c r="B33" t="n">
         <v>99295</v>
@@ -4289,13 +4251,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481716</v>
+        <v>481646</v>
       </c>
       <c r="R33" t="n">
-        <v>7024780</v>
+        <v>7024891</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4324,7 +4286,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4334,7 +4296,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,13 +4322,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574656</v>
+        <v>135574672</v>
       </c>
       <c r="B34" t="n">
         <v>99295</v>
@@ -4401,13 +4363,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481734</v>
+        <v>481561</v>
       </c>
       <c r="R34" t="n">
-        <v>7024791</v>
+        <v>7024902</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4398,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4408,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,13 +4434,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574660</v>
+        <v>135574674</v>
       </c>
       <c r="B35" t="n">
         <v>99295</v>
@@ -4513,13 +4475,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481719</v>
+        <v>481578</v>
       </c>
       <c r="R35" t="n">
-        <v>7024855</v>
+        <v>7024883</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4548,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4558,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4584,13 +4546,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574661</v>
+        <v>135574676</v>
       </c>
       <c r="B36" t="n">
         <v>99295</v>
@@ -4625,13 +4587,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481701</v>
+        <v>481552</v>
       </c>
       <c r="R36" t="n">
-        <v>7024856</v>
+        <v>7024876</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4660,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4670,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4696,13 +4658,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574663</v>
+        <v>135574680</v>
       </c>
       <c r="B37" t="n">
         <v>99295</v>
@@ -4737,13 +4699,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481646</v>
+        <v>481573</v>
       </c>
       <c r="R37" t="n">
-        <v>7024891</v>
+        <v>7024817</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4772,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4782,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4808,13 +4770,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574672</v>
+        <v>135574684</v>
       </c>
       <c r="B38" t="n">
         <v>99295</v>
@@ -4849,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481561</v>
+        <v>481498</v>
       </c>
       <c r="R38" t="n">
-        <v>7024902</v>
+        <v>7024750</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4884,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4894,7 +4856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4920,13 +4882,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574674</v>
+        <v>135574688</v>
       </c>
       <c r="B39" t="n">
         <v>99295</v>
@@ -4961,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481578</v>
+        <v>481456</v>
       </c>
       <c r="R39" t="n">
-        <v>7024883</v>
+        <v>7024666</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4996,7 +4958,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5006,7 +4968,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5032,13 +4994,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574676</v>
+        <v>135574689</v>
       </c>
       <c r="B40" t="n">
         <v>99295</v>
@@ -5073,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481552</v>
+        <v>481438</v>
       </c>
       <c r="R40" t="n">
-        <v>7024876</v>
+        <v>7024662</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5108,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5118,7 +5080,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,13 +5106,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574680</v>
+        <v>135574691</v>
       </c>
       <c r="B41" t="n">
         <v>99295</v>
@@ -5185,13 +5147,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481573</v>
+        <v>481402</v>
       </c>
       <c r="R41" t="n">
-        <v>7024817</v>
+        <v>7024646</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5220,7 +5182,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5230,7 +5192,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5256,13 +5218,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574684</v>
+        <v>135574692</v>
       </c>
       <c r="B42" t="n">
         <v>99295</v>
@@ -5297,13 +5259,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481498</v>
+        <v>481397</v>
       </c>
       <c r="R42" t="n">
-        <v>7024750</v>
+        <v>7024634</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5332,7 +5294,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5342,7 +5304,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5368,38 +5330,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574688</v>
+        <v>135574635</v>
       </c>
       <c r="B43" t="n">
-        <v>99295</v>
+        <v>101505</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5409,10 +5371,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481456</v>
+        <v>481524</v>
       </c>
       <c r="R43" t="n">
-        <v>7024666</v>
+        <v>7024657</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5444,7 +5406,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5454,7 +5416,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,38 +5442,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574689</v>
+        <v>135574640</v>
       </c>
       <c r="B44" t="n">
-        <v>99295</v>
+        <v>101505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5521,13 +5483,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481438</v>
+        <v>481545</v>
       </c>
       <c r="R44" t="n">
-        <v>7024662</v>
+        <v>7024654</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5556,7 +5518,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5566,7 +5528,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5592,38 +5554,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574691</v>
+        <v>135574645</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>101505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5633,13 +5595,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481402</v>
+        <v>481577</v>
       </c>
       <c r="R45" t="n">
-        <v>7024646</v>
+        <v>7024692</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5668,7 +5630,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5678,7 +5640,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5704,38 +5666,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574692</v>
+        <v>135574649</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>101505</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5745,13 +5707,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481397</v>
+        <v>481625</v>
       </c>
       <c r="R46" t="n">
-        <v>7024634</v>
+        <v>7024693</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5780,7 +5742,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5790,7 +5752,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,13 +5778,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574635</v>
+        <v>135574654</v>
       </c>
       <c r="B47" t="n">
         <v>101505</v>
@@ -5857,10 +5819,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481524</v>
+        <v>481705</v>
       </c>
       <c r="R47" t="n">
-        <v>7024657</v>
+        <v>7024756</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5892,7 +5854,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5902,7 +5864,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5928,13 +5890,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574640</v>
+        <v>135574657</v>
       </c>
       <c r="B48" t="n">
         <v>101505</v>
@@ -5969,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481545</v>
+        <v>481729</v>
       </c>
       <c r="R48" t="n">
-        <v>7024654</v>
+        <v>7024823</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6004,7 +5966,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6014,7 +5976,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6040,13 +6002,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574645</v>
+        <v>135574659</v>
       </c>
       <c r="B49" t="n">
         <v>101505</v>
@@ -6081,10 +6043,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481577</v>
+        <v>481714</v>
       </c>
       <c r="R49" t="n">
-        <v>7024692</v>
+        <v>7024855</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6116,7 +6078,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6126,7 +6088,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6152,13 +6114,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574649</v>
+        <v>135574667</v>
       </c>
       <c r="B50" t="n">
         <v>101505</v>
@@ -6193,10 +6155,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481625</v>
+        <v>481606</v>
       </c>
       <c r="R50" t="n">
-        <v>7024693</v>
+        <v>7024919</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6228,7 +6190,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6238,7 +6200,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,13 +6226,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574654</v>
+        <v>135574673</v>
       </c>
       <c r="B51" t="n">
         <v>101505</v>
@@ -6305,13 +6267,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481705</v>
+        <v>481558</v>
       </c>
       <c r="R51" t="n">
-        <v>7024756</v>
+        <v>7024899</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6340,7 +6302,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6350,7 +6312,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6376,13 +6338,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574673</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574657</v>
+        <v>135574678</v>
       </c>
       <c r="B52" t="n">
         <v>101505</v>
@@ -6417,10 +6379,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481729</v>
+        <v>481581</v>
       </c>
       <c r="R52" t="n">
-        <v>7024823</v>
+        <v>7024835</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6452,7 +6414,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6462,7 +6424,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6488,13 +6450,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574678</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574659</v>
+        <v>135574681</v>
       </c>
       <c r="B53" t="n">
         <v>101505</v>
@@ -6529,10 +6491,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481714</v>
+        <v>481566</v>
       </c>
       <c r="R53" t="n">
-        <v>7024855</v>
+        <v>7024806</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6564,7 +6526,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6574,7 +6536,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6600,13 +6562,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574681</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574667</v>
+        <v>135574685</v>
       </c>
       <c r="B54" t="n">
         <v>101505</v>
@@ -6641,13 +6603,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481606</v>
+        <v>481499</v>
       </c>
       <c r="R54" t="n">
-        <v>7024919</v>
+        <v>7024746</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6676,7 +6638,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6686,7 +6648,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6712,16 +6674,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574685</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574673</v>
+        <v>135574682</v>
       </c>
       <c r="B55" t="n">
-        <v>101505</v>
+        <v>99572</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6729,21 +6691,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>222812</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6753,13 +6715,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481558</v>
+        <v>481541</v>
       </c>
       <c r="R55" t="n">
-        <v>7024899</v>
+        <v>7024804</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6788,7 +6750,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6798,7 +6760,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6823,454 +6785,6 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135574678</v>
-      </c>
-      <c r="B56" t="n">
-        <v>101505</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>481581</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7024835</v>
-      </c>
-      <c r="S56" t="n">
-        <v>4</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135574681</v>
-      </c>
-      <c r="B57" t="n">
-        <v>101505</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>481566</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7024806</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135574685</v>
-      </c>
-      <c r="B58" t="n">
-        <v>101505</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>481499</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7024746</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135574682</v>
-      </c>
-      <c r="B59" t="n">
-        <v>99572</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Hånåberget N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>481541</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7024804</v>
-      </c>
-      <c r="S59" t="n">
-        <v>4</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -7332,10 +6846,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26176-2026 artfynd.xlsx
+++ b/artfynd/A 26176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135574690</v>
+        <v>135574666</v>
       </c>
       <c r="B17" t="n">
-        <v>58086</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,36 +2431,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481438</v>
+        <v>481606</v>
       </c>
       <c r="R17" t="n">
-        <v>7024659</v>
+        <v>7024919</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2487,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,54 +2518,59 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574690</t>
+          <t>https://artportalen.se/Sighting/135574666</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135574638</v>
+        <v>135574668</v>
       </c>
       <c r="B18" t="n">
-        <v>99212</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481544</v>
+        <v>481600</v>
       </c>
       <c r="R18" t="n">
-        <v>7024650</v>
+        <v>7024916</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2609,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,54 +2640,58 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574638</t>
+          <t>https://artportalen.se/Sighting/135574668</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135574643</v>
+        <v>135574670</v>
       </c>
       <c r="B19" t="n">
-        <v>99212</v>
+        <v>58006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481579</v>
+        <v>481586</v>
       </c>
       <c r="R19" t="n">
-        <v>7024692</v>
+        <v>7024911</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2713,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2730,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,51 +2761,56 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574643</t>
+          <t>https://artportalen.se/Sighting/135574670</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135574634</v>
+        <v>135574677</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>58006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481508</v>
+        <v>481568</v>
       </c>
       <c r="R20" t="n">
-        <v>7024656</v>
+        <v>7024870</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2825,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2852,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,54 +2883,70 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574634</t>
+          <t>https://artportalen.se/Sighting/135574677</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135574639</v>
+        <v>135574690</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>58086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåberget N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481525</v>
+        <v>481438</v>
       </c>
       <c r="R21" t="n">
-        <v>7024642</v>
+        <v>7024659</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2937,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2985,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,38 +3011,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574639</t>
+          <t>https://artportalen.se/Sighting/135574690</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135574641</v>
+        <v>135574638</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3052,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481577</v>
+        <v>481544</v>
       </c>
       <c r="R22" t="n">
-        <v>7024669</v>
+        <v>7024650</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3049,7 +3087,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3097,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,38 +3123,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574641</t>
+          <t>https://artportalen.se/Sighting/135574638</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135574644</v>
+        <v>135574643</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,13 +3164,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481577</v>
+        <v>481579</v>
       </c>
       <c r="R23" t="n">
-        <v>7024691</v>
+        <v>7024692</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3161,7 +3199,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3209,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,13 +3235,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574644</t>
+          <t>https://artportalen.se/Sighting/135574643</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135574647</v>
+        <v>135574634</v>
       </c>
       <c r="B24" t="n">
         <v>99295</v>
@@ -3238,13 +3276,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481595</v>
+        <v>481508</v>
       </c>
       <c r="R24" t="n">
-        <v>7024696</v>
+        <v>7024656</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3273,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,13 +3347,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574647</t>
+          <t>https://artportalen.se/Sighting/135574634</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135574648</v>
+        <v>135574639</v>
       </c>
       <c r="B25" t="n">
         <v>99295</v>
@@ -3350,13 +3388,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481630</v>
+        <v>481525</v>
       </c>
       <c r="R25" t="n">
-        <v>7024686</v>
+        <v>7024642</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3385,7 +3423,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3433,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,13 +3459,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574648</t>
+          <t>https://artportalen.se/Sighting/135574639</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135574650</v>
+        <v>135574641</v>
       </c>
       <c r="B26" t="n">
         <v>99295</v>
@@ -3462,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>481647</v>
+        <v>481577</v>
       </c>
       <c r="R26" t="n">
-        <v>7024696</v>
+        <v>7024669</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3497,7 +3535,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3507,12 +3545,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,13 +3571,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574650</t>
+          <t>https://artportalen.se/Sighting/135574641</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135574651</v>
+        <v>135574644</v>
       </c>
       <c r="B27" t="n">
         <v>99295</v>
@@ -3579,13 +3612,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>481676</v>
+        <v>481577</v>
       </c>
       <c r="R27" t="n">
-        <v>7024717</v>
+        <v>7024691</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3614,7 +3647,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3624,7 +3657,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,13 +3683,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574651</t>
+          <t>https://artportalen.se/Sighting/135574644</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135574652</v>
+        <v>135574647</v>
       </c>
       <c r="B28" t="n">
         <v>99295</v>
@@ -3691,13 +3724,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481695</v>
+        <v>481595</v>
       </c>
       <c r="R28" t="n">
-        <v>7024735</v>
+        <v>7024696</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3726,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3769,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3762,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574652</t>
+          <t>https://artportalen.se/Sighting/135574647</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135574655</v>
+        <v>135574648</v>
       </c>
       <c r="B29" t="n">
         <v>99295</v>
@@ -3803,10 +3836,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481716</v>
+        <v>481630</v>
       </c>
       <c r="R29" t="n">
-        <v>7024780</v>
+        <v>7024686</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3838,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3848,7 +3881,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3874,13 +3907,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574655</t>
+          <t>https://artportalen.se/Sighting/135574648</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135574656</v>
+        <v>135574650</v>
       </c>
       <c r="B30" t="n">
         <v>99295</v>
@@ -3915,13 +3948,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481734</v>
+        <v>481647</v>
       </c>
       <c r="R30" t="n">
-        <v>7024791</v>
+        <v>7024696</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3950,7 +3983,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3960,7 +3993,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,13 +4024,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574656</t>
+          <t>https://artportalen.se/Sighting/135574650</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135574660</v>
+        <v>135574651</v>
       </c>
       <c r="B31" t="n">
         <v>99295</v>
@@ -4027,13 +4065,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481719</v>
+        <v>481676</v>
       </c>
       <c r="R31" t="n">
-        <v>7024855</v>
+        <v>7024717</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,7 +4100,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4110,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4098,13 +4136,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574660</t>
+          <t>https://artportalen.se/Sighting/135574651</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135574661</v>
+        <v>135574652</v>
       </c>
       <c r="B32" t="n">
         <v>99295</v>
@@ -4139,13 +4177,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481701</v>
+        <v>481695</v>
       </c>
       <c r="R32" t="n">
-        <v>7024856</v>
+        <v>7024735</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4174,7 +4212,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +4222,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4210,13 +4248,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574661</t>
+          <t>https://artportalen.se/Sighting/135574652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135574663</v>
+        <v>135574655</v>
       </c>
       <c r="B33" t="n">
         <v>99295</v>
@@ -4251,13 +4289,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481646</v>
+        <v>481716</v>
       </c>
       <c r="R33" t="n">
-        <v>7024891</v>
+        <v>7024780</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4286,7 +4324,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4296,7 +4334,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,13 +4360,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574663</t>
+          <t>https://artportalen.se/Sighting/135574655</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135574672</v>
+        <v>135574656</v>
       </c>
       <c r="B34" t="n">
         <v>99295</v>
@@ -4363,13 +4401,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481561</v>
+        <v>481734</v>
       </c>
       <c r="R34" t="n">
-        <v>7024902</v>
+        <v>7024791</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4398,7 +4436,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4408,7 +4446,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4434,13 +4472,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574672</t>
+          <t>https://artportalen.se/Sighting/135574656</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135574674</v>
+        <v>135574660</v>
       </c>
       <c r="B35" t="n">
         <v>99295</v>
@@ -4475,13 +4513,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481578</v>
+        <v>481719</v>
       </c>
       <c r="R35" t="n">
-        <v>7024883</v>
+        <v>7024855</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4510,7 +4548,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4558,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4546,13 +4584,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574674</t>
+          <t>https://artportalen.se/Sighting/135574660</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135574676</v>
+        <v>135574661</v>
       </c>
       <c r="B36" t="n">
         <v>99295</v>
@@ -4587,13 +4625,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481552</v>
+        <v>481701</v>
       </c>
       <c r="R36" t="n">
-        <v>7024876</v>
+        <v>7024856</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4622,7 +4660,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4670,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4658,13 +4696,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574676</t>
+          <t>https://artportalen.se/Sighting/135574661</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135574680</v>
+        <v>135574663</v>
       </c>
       <c r="B37" t="n">
         <v>99295</v>
@@ -4699,13 +4737,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481573</v>
+        <v>481646</v>
       </c>
       <c r="R37" t="n">
-        <v>7024817</v>
+        <v>7024891</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4734,7 +4772,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4782,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4770,13 +4808,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574680</t>
+          <t>https://artportalen.se/Sighting/135574663</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135574684</v>
+        <v>135574672</v>
       </c>
       <c r="B38" t="n">
         <v>99295</v>
@@ -4811,10 +4849,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481498</v>
+        <v>481561</v>
       </c>
       <c r="R38" t="n">
-        <v>7024750</v>
+        <v>7024902</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4846,7 +4884,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4894,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4882,13 +4920,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574684</t>
+          <t>https://artportalen.se/Sighting/135574672</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135574688</v>
+        <v>135574674</v>
       </c>
       <c r="B39" t="n">
         <v>99295</v>
@@ -4923,10 +4961,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481456</v>
+        <v>481578</v>
       </c>
       <c r="R39" t="n">
-        <v>7024666</v>
+        <v>7024883</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4958,7 +4996,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +5006,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,13 +5032,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574688</t>
+          <t>https://artportalen.se/Sighting/135574674</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135574689</v>
+        <v>135574676</v>
       </c>
       <c r="B40" t="n">
         <v>99295</v>
@@ -5035,10 +5073,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481438</v>
+        <v>481552</v>
       </c>
       <c r="R40" t="n">
-        <v>7024662</v>
+        <v>7024876</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5070,7 +5108,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,7 +5118,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5106,13 +5144,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574689</t>
+          <t>https://artportalen.se/Sighting/135574676</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135574691</v>
+        <v>135574680</v>
       </c>
       <c r="B41" t="n">
         <v>99295</v>
@@ -5147,13 +5185,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481402</v>
+        <v>481573</v>
       </c>
       <c r="R41" t="n">
-        <v>7024646</v>
+        <v>7024817</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5182,7 +5220,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5192,7 +5230,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5218,13 +5256,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574691</t>
+          <t>https://artportalen.se/Sighting/135574680</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135574692</v>
+        <v>135574684</v>
       </c>
       <c r="B42" t="n">
         <v>99295</v>
@@ -5259,13 +5297,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481397</v>
+        <v>481498</v>
       </c>
       <c r="R42" t="n">
-        <v>7024634</v>
+        <v>7024750</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5294,7 +5332,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5304,7 +5342,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,38 +5368,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574692</t>
+          <t>https://artportalen.se/Sighting/135574684</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135574635</v>
+        <v>135574688</v>
       </c>
       <c r="B43" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5371,10 +5409,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481524</v>
+        <v>481456</v>
       </c>
       <c r="R43" t="n">
-        <v>7024657</v>
+        <v>7024666</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5406,7 +5444,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5416,7 +5454,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5442,38 +5480,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574635</t>
+          <t>https://artportalen.se/Sighting/135574688</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135574640</v>
+        <v>135574689</v>
       </c>
       <c r="B44" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5483,13 +5521,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481545</v>
+        <v>481438</v>
       </c>
       <c r="R44" t="n">
-        <v>7024654</v>
+        <v>7024662</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5518,7 +5556,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5528,7 +5566,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5554,38 +5592,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574640</t>
+          <t>https://artportalen.se/Sighting/135574689</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135574645</v>
+        <v>135574691</v>
       </c>
       <c r="B45" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,13 +5633,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481577</v>
+        <v>481402</v>
       </c>
       <c r="R45" t="n">
-        <v>7024692</v>
+        <v>7024646</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5630,7 +5668,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5640,7 +5678,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,38 +5704,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574645</t>
+          <t>https://artportalen.se/Sighting/135574691</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135574649</v>
+        <v>135574692</v>
       </c>
       <c r="B46" t="n">
-        <v>101505</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5707,13 +5745,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481625</v>
+        <v>481397</v>
       </c>
       <c r="R46" t="n">
-        <v>7024693</v>
+        <v>7024634</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5742,7 +5780,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5752,7 +5790,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,13 +5816,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574649</t>
+          <t>https://artportalen.se/Sighting/135574692</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135574654</v>
+        <v>135574635</v>
       </c>
       <c r="B47" t="n">
         <v>101505</v>
@@ -5819,10 +5857,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481705</v>
+        <v>481524</v>
       </c>
       <c r="R47" t="n">
-        <v>7024756</v>
+        <v>7024657</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5854,7 +5892,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5864,7 +5902,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5890,13 +5928,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574654</t>
+          <t>https://artportalen.se/Sighting/135574635</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135574657</v>
+        <v>135574640</v>
       </c>
       <c r="B48" t="n">
         <v>101505</v>
@@ -5931,10 +5969,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481729</v>
+        <v>481545</v>
       </c>
       <c r="R48" t="n">
-        <v>7024823</v>
+        <v>7024654</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5966,7 +6004,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5976,7 +6014,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6002,13 +6040,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574657</t>
+          <t>https://artportalen.se/Sighting/135574640</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135574659</v>
+        <v>135574645</v>
       </c>
       <c r="B49" t="n">
         <v>101505</v>
@@ -6043,10 +6081,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481714</v>
+        <v>481577</v>
       </c>
       <c r="R49" t="n">
-        <v>7024855</v>
+        <v>7024692</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -6078,7 +6116,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6088,7 +6126,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6114,13 +6152,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574659</t>
+          <t>https://artportalen.se/Sighting/135574645</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135574667</v>
+        <v>135574649</v>
       </c>
       <c r="B50" t="n">
         <v>101505</v>
@@ -6155,10 +6193,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481606</v>
+        <v>481625</v>
       </c>
       <c r="R50" t="n">
-        <v>7024919</v>
+        <v>7024693</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -6190,7 +6228,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6200,7 +6238,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6226,13 +6264,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574667</t>
+          <t>https://artportalen.se/Sighting/135574649</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135574673</v>
+        <v>135574654</v>
       </c>
       <c r="B51" t="n">
         <v>101505</v>
@@ -6267,13 +6305,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481558</v>
+        <v>481705</v>
       </c>
       <c r="R51" t="n">
-        <v>7024899</v>
+        <v>7024756</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6302,7 +6340,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6312,7 +6350,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6338,13 +6376,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574673</t>
+          <t>https://artportalen.se/Sighting/135574654</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135574678</v>
+        <v>135574657</v>
       </c>
       <c r="B52" t="n">
         <v>101505</v>
@@ -6379,10 +6417,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481581</v>
+        <v>481729</v>
       </c>
       <c r="R52" t="n">
-        <v>7024835</v>
+        <v>7024823</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6414,7 +6452,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6424,7 +6462,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6450,13 +6488,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574678</t>
+          <t>https://artportalen.se/Sighting/135574657</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135574681</v>
+        <v>135574659</v>
       </c>
       <c r="B53" t="n">
         <v>101505</v>
@@ -6491,10 +6529,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481566</v>
+        <v>481714</v>
       </c>
       <c r="R53" t="n">
-        <v>7024806</v>
+        <v>7024855</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6526,7 +6564,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6536,7 +6574,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6562,13 +6600,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574681</t>
+          <t>https://artportalen.se/Sighting/135574659</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135574685</v>
+        <v>135574667</v>
       </c>
       <c r="B54" t="n">
         <v>101505</v>
@@ -6603,13 +6641,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481499</v>
+        <v>481606</v>
       </c>
       <c r="R54" t="n">
-        <v>7024746</v>
+        <v>7024919</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6638,7 +6676,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6648,7 +6686,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6674,16 +6712,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135574685</t>
+          <t>https://artportalen.se/Sighting/135574667</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135574682</v>
+        <v>135574673</v>
       </c>
       <c r="B55" t="n">
-        <v>99572</v>
+        <v>101505</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6691,21 +6729,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,13 +6753,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481541</v>
+        <v>481558</v>
       </c>
       <c r="R55" t="n">
-        <v>7024804</v>
+        <v>7024899</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6750,7 +6788,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6760,7 +6798,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6785,6 +6823,454 @@
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574673</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135574678</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>481581</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7024835</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574678</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135574681</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>481566</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7024806</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574681</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135574685</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>481499</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7024746</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135574685</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135574682</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99572</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hånåberget N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>481541</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7024804</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135574682</t>
         </is>
@@ -6846,6 +7332,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
